--- a/data/FRS_cleaned/Nov/Fmn D Nov/WorkOrderRemote_Nov 2025 D.xlsx
+++ b/data/FRS_cleaned/Nov/Fmn D Nov/WorkOrderRemote_Nov 2025 D.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\fwDemo\data\FRS_cleaned\Nov\Fmn D Nov\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Anu\APT\apt\army\fortwilliam\code\fwDemo\data\FRS_cleaned\Nov\Fmn D Nov\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BA53988-144D-4487-B371-F863C92A1BEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{009EB9EF-2D17-4F68-92B9-63ACE4C9AAF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30" yWindow="-16170" windowWidth="28800" windowHeight="15195" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Eng" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="168">
   <si>
     <r>
       <rPr>
@@ -4819,10 +4819,89 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1C1D1C"/>
+    <t>Veh BA No</t>
+  </si>
+  <si>
+    <t>Remarks</t>
+  </si>
+  <si>
+    <t>A2</t>
+  </si>
+  <si>
+    <t>U8</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF363836"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>89X 6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>111M</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF363836"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">89X </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>583</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF363836"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>P</t>
+    </r>
+  </si>
+  <si>
+    <t>Universal Joint</t>
+  </si>
+  <si>
+    <t>F1</t>
+  </si>
+  <si>
+    <t>Under collection</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030303"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -4831,613 +4910,444 @@
     <r>
       <rPr>
         <sz val="10"/>
+        <color rgb="FF1C1D1C"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>on</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <color rgb="FF030303"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
+      <t>tro</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF363634"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">l </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1C1D1C"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>date</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF363836"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>HI</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF363836"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>H1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>F</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF363836"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>l</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>H</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>I</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>H1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>H</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>e</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">rt </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>B</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ase </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF363836"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>D</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>isposa</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">l </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Mech</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Ro</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>t</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>or</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>b</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">lower </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
       <t>a</t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
-        <color rgb="FF1C1D1C"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>tego</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030303"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ry  </t>
-    </r>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>n</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">d </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ge</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ar </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>sel Cons</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF363836"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>i</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF363836"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>t o</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">f 5 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF030503"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>I</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>tems</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>424Q.000107</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1D1F1D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>A5</t>
+    </r>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>Formation</t>
+  </si>
+  <si>
+    <t>A6</t>
+  </si>
+  <si>
+    <t>A1</t>
+  </si>
+  <si>
+    <t>A3</t>
+  </si>
+  <si>
+    <t>A4</t>
+  </si>
+  <si>
+    <t>A7</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
         <sz val="10"/>
-        <color rgb="FF030303"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>(Make and Type)</t>
-    </r>
-  </si>
-  <si>
-    <t>Veh BA No</t>
-  </si>
-  <si>
-    <t>Remarks</t>
-  </si>
-  <si>
-    <t>A2</t>
-  </si>
-  <si>
-    <t>U8</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF363836"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>89X 6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>111M</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF363836"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">89X </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>583</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF363836"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>P</t>
-    </r>
-  </si>
-  <si>
-    <t>Universal Joint</t>
-  </si>
-  <si>
-    <t>F1</t>
-  </si>
-  <si>
-    <t>Under collection</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030303"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1C1D1C"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>on</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030303"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>tro</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF363634"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">l </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1C1D1C"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>date</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF363836"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>HI</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF363836"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>H1</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>F</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF363836"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>l</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>H</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>I</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>H1</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>H</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>1</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>C</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>e</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">rt </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>B</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ase </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF363836"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>D</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>isposa</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">l </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Mech</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Ro</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>t</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>or</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>b</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">lower </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>a</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>n</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">d </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>ge</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ar </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>sel Cons</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF363836"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>i</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>s</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF363836"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>t o</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">f 5 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>I</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>tems</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>424Q.000107</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>A5</t>
-    </r>
-  </si>
-  <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>Formation</t>
-  </si>
-  <si>
-    <t>A6</t>
-  </si>
-  <si>
-    <t>A1</t>
-  </si>
-  <si>
-    <t>A3</t>
-  </si>
-  <si>
-    <t>A4</t>
-  </si>
-  <si>
-    <t>A7</t>
-  </si>
-  <si>
+        <color rgb="FF1C1D1C"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>S</t>
+    </r>
     <r>
       <rPr>
         <b/>
         <sz val="10"/>
-        <color rgb="FF1C1D1C"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>S</t>
+        <color rgb="FF757774"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
     </r>
     <r>
       <rPr>
         <b/>
         <sz val="10"/>
-        <color rgb="FF757774"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
         <color rgb="FF1C1D1C"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
       <t>No</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF1C1D1C"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>C</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF030303"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>a</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF1C1D1C"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>tego</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color rgb="FF030303"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>ry  (Make and Type)</t>
     </r>
   </si>
   <si>
@@ -6453,6 +6363,9 @@
       </rPr>
       <t>)</t>
     </r>
+  </si>
+  <si>
+    <t>Category</t>
   </si>
 </sst>
 </file>
@@ -6460,8 +6373,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="165" formatCode="0.000000"/>
-    <numFmt numFmtId="167" formatCode="[$-14009]dd/mm/yyyy;@"/>
+    <numFmt numFmtId="164" formatCode="0.000000"/>
+    <numFmt numFmtId="165" formatCode="[$-14009]dd/mm/yyyy;@"/>
   </numFmts>
   <fonts count="25" x14ac:knownFonts="1">
     <font>
@@ -6753,7 +6666,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -6802,7 +6715,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -6982,40 +6895,43 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -7324,35 +7240,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15BF3CFF-B171-44D9-B5BE-3C4491948958}">
   <dimension ref="A1:O5"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="10.5" customWidth="1"/>
+    <col min="2" max="2" width="10.44140625" customWidth="1"/>
     <col min="3" max="3" width="23.33203125" customWidth="1"/>
-    <col min="5" max="5" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.77734375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="25.33203125" customWidth="1"/>
-    <col min="8" max="8" width="50.5" customWidth="1"/>
-    <col min="10" max="10" width="22.83203125" customWidth="1"/>
-    <col min="11" max="11" width="14.1640625" style="86" customWidth="1"/>
-    <col min="12" max="12" width="14.83203125" customWidth="1"/>
+    <col min="8" max="8" width="50.44140625" customWidth="1"/>
+    <col min="10" max="10" width="22.77734375" customWidth="1"/>
+    <col min="11" max="11" width="14.109375" style="86" customWidth="1"/>
+    <col min="12" max="12" width="14.77734375" customWidth="1"/>
     <col min="13" max="13" width="14.33203125" style="86" customWidth="1"/>
     <col min="15" max="15" width="46.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="29" t="s">
+        <v>167</v>
+      </c>
+      <c r="C1" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="C1" s="30" t="s">
-        <v>107</v>
-      </c>
       <c r="D1" s="31" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E1" s="74" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F1" s="21" t="s">
         <v>1</v>
@@ -7376,33 +7292,33 @@
         <v>7</v>
       </c>
       <c r="M1" s="83" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N1" s="26" t="s">
         <v>8</v>
       </c>
       <c r="O1" s="18" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
-    <row r="2" spans="1:15" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="19">
         <v>1</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C2" s="25" t="s">
         <v>9</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F2" s="22" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -7432,7 +7348,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:15" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="27">
         <v>2</v>
       </c>
@@ -7443,13 +7359,13 @@
         <v>18</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F3" s="22" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G3" s="11" t="s">
         <v>19</v>
@@ -7479,7 +7395,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:15" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="28">
         <v>3</v>
       </c>
@@ -7490,13 +7406,13 @@
         <v>26</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E4" s="21" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F4" s="22" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G4" s="11" t="s">
         <v>27</v>
@@ -7526,24 +7442,24 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:15" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="28">
         <v>4</v>
       </c>
       <c r="B5" s="32" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C5" s="24" t="s">
         <v>31</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F5" s="22" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G5" s="11" t="s">
         <v>32</v>
@@ -7581,44 +7497,44 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B2C714C-5842-4352-8784-DCBCFC842B13}">
   <dimension ref="A1:O17"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.33203125" style="65"/>
     <col min="2" max="2" width="14" style="65" customWidth="1"/>
-    <col min="3" max="3" width="19.5" style="65" customWidth="1"/>
-    <col min="4" max="4" width="13.83203125" style="65" customWidth="1"/>
+    <col min="3" max="3" width="19.44140625" style="65" customWidth="1"/>
+    <col min="4" max="4" width="13.77734375" style="65" customWidth="1"/>
     <col min="5" max="5" width="15.6640625" style="65" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.6640625" style="65" customWidth="1"/>
     <col min="7" max="7" width="32.6640625" style="65" customWidth="1"/>
-    <col min="8" max="8" width="44.5" style="65" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="44.44140625" style="65" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.33203125" style="65"/>
     <col min="10" max="10" width="33.33203125" style="65" customWidth="1"/>
     <col min="11" max="11" width="14" style="82" customWidth="1"/>
     <col min="12" max="12" width="15.6640625" style="65" customWidth="1"/>
-    <col min="13" max="13" width="14.83203125" style="82" customWidth="1"/>
+    <col min="13" max="13" width="14.77734375" style="82" customWidth="1"/>
     <col min="14" max="14" width="9.33203125" style="65"/>
-    <col min="15" max="15" width="60.1640625" style="65" customWidth="1"/>
+    <col min="15" max="15" width="60.109375" style="65" customWidth="1"/>
     <col min="16" max="16384" width="9.33203125" style="65"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="63" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" s="63" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="49" t="s">
+        <v>133</v>
+      </c>
+      <c r="B1" s="50" t="s">
+        <v>167</v>
+      </c>
+      <c r="C1" s="62" t="s">
+        <v>106</v>
+      </c>
+      <c r="D1" s="51" t="s">
+        <v>127</v>
+      </c>
+      <c r="E1" s="75" t="s">
+        <v>149</v>
+      </c>
+      <c r="F1" s="52" t="s">
         <v>134</v>
-      </c>
-      <c r="B1" s="50" t="s">
-        <v>135</v>
-      </c>
-      <c r="C1" s="62" t="s">
-        <v>107</v>
-      </c>
-      <c r="D1" s="51" t="s">
-        <v>128</v>
-      </c>
-      <c r="E1" s="75" t="s">
-        <v>151</v>
-      </c>
-      <c r="F1" s="52" t="s">
-        <v>136</v>
       </c>
       <c r="G1" s="52" t="s">
         <v>2</v>
@@ -7627,51 +7543,51 @@
         <v>3</v>
       </c>
       <c r="I1" s="53" t="s">
+        <v>135</v>
+      </c>
+      <c r="J1" s="52" t="s">
+        <v>136</v>
+      </c>
+      <c r="K1" s="76" t="s">
         <v>137</v>
       </c>
-      <c r="J1" s="52" t="s">
+      <c r="L1" s="49" t="s">
         <v>138</v>
       </c>
-      <c r="K1" s="76" t="s">
+      <c r="M1" s="76" t="s">
         <v>139</v>
-      </c>
-      <c r="L1" s="49" t="s">
-        <v>140</v>
-      </c>
-      <c r="M1" s="76" t="s">
-        <v>141</v>
       </c>
       <c r="N1" s="52" t="s">
         <v>8</v>
       </c>
       <c r="O1" s="61" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="39">
         <v>1</v>
       </c>
       <c r="B2" s="35" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C2" s="34" t="s">
         <v>51</v>
       </c>
       <c r="D2" s="41" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E2" s="34" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F2" s="41" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G2" s="34" t="s">
         <v>52</v>
       </c>
       <c r="H2" s="44" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I2" s="39">
         <v>1</v>
@@ -7689,30 +7605,30 @@
         <v>45814</v>
       </c>
       <c r="N2" s="42" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="O2" s="64" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="37">
         <v>2</v>
       </c>
       <c r="B3" s="35" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C3" s="34" t="s">
         <v>62</v>
       </c>
       <c r="D3" s="41" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E3" s="41" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F3" s="41" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G3" s="34" t="s">
         <v>63</v>
@@ -7736,11 +7652,11 @@
         <v>45453</v>
       </c>
       <c r="N3" s="42" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O3" s="64"/>
     </row>
-    <row r="4" spans="1:15" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="39">
         <v>3</v>
       </c>
@@ -7751,16 +7667,16 @@
         <v>67</v>
       </c>
       <c r="D4" s="41" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E4" s="34" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F4" s="41" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G4" s="44" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H4" s="34" t="s">
         <v>68</v>
@@ -7769,7 +7685,7 @@
         <v>1</v>
       </c>
       <c r="J4" s="45" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="K4" s="78">
         <v>45593</v>
@@ -7781,13 +7697,13 @@
         <v>45609</v>
       </c>
       <c r="N4" s="42" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O4" s="64" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>4</v>
       </c>
@@ -7795,16 +7711,16 @@
         <v>69</v>
       </c>
       <c r="C5" s="44" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D5" s="41" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E5" s="34" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F5" s="41" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G5" s="34" t="s">
         <v>70</v>
@@ -7828,30 +7744,30 @@
         <v>45609</v>
       </c>
       <c r="N5" s="42" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="O5" s="64" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="39">
         <v>5</v>
       </c>
       <c r="B6" s="35" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C6" s="34" t="s">
         <v>58</v>
       </c>
       <c r="D6" s="41" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E6" s="34" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F6" s="41" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G6" s="34" t="s">
         <v>59</v>
@@ -7875,11 +7791,11 @@
         <v>45453</v>
       </c>
       <c r="N6" s="42" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O6" s="64"/>
     </row>
-    <row r="7" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="37">
         <v>6</v>
       </c>
@@ -7890,19 +7806,19 @@
         <v>73</v>
       </c>
       <c r="D7" s="41" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E7" s="34" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F7" s="41" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G7" s="34" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="H7" s="44" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I7" s="36">
         <v>1</v>
@@ -7920,28 +7836,28 @@
         <v>75</v>
       </c>
       <c r="N7" s="42" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="O7" s="64"/>
     </row>
-    <row r="8" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="39">
         <v>7</v>
       </c>
       <c r="B8" s="35" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C8" s="34" t="s">
         <v>76</v>
       </c>
       <c r="D8" s="41" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E8" s="34" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F8" s="41" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G8" s="34" t="s">
         <v>77</v>
@@ -7965,31 +7881,31 @@
         <v>75</v>
       </c>
       <c r="N8" s="42" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O8" s="64"/>
     </row>
-    <row r="9" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="37">
         <v>8</v>
       </c>
       <c r="B9" s="35" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C9" s="34" t="s">
         <v>81</v>
       </c>
       <c r="D9" s="41" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F9" s="41" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G9" s="34" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H9" s="34" t="s">
         <v>82</v>
@@ -8010,28 +7926,28 @@
         <v>45717</v>
       </c>
       <c r="N9" s="42" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O9" s="64"/>
     </row>
-    <row r="10" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="39">
         <v>9</v>
       </c>
       <c r="B10" s="35" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C10" s="34" t="s">
         <v>84</v>
       </c>
       <c r="D10" s="41" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E10" s="41" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F10" s="41" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G10" s="34" t="s">
         <v>85</v>
@@ -8055,33 +7971,33 @@
         <v>45717</v>
       </c>
       <c r="N10" s="42" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O10" s="64" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="37">
         <v>10</v>
       </c>
       <c r="B11" s="34" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C11" s="34" t="s">
         <v>88</v>
       </c>
       <c r="D11" s="41" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E11" s="34" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F11" s="41" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G11" s="34" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H11" s="34" t="s">
         <v>89</v>
@@ -8102,28 +8018,28 @@
         <v>45719</v>
       </c>
       <c r="N11" s="42" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O11" s="64"/>
     </row>
-    <row r="12" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="39">
         <v>11</v>
       </c>
       <c r="B12" s="34" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C12" s="34" t="s">
         <v>91</v>
       </c>
       <c r="D12" s="41" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E12" s="34" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F12" s="41" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G12" s="34" t="s">
         <v>92</v>
@@ -8147,28 +8063,28 @@
         <v>45735</v>
       </c>
       <c r="N12" s="42" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O12" s="64"/>
     </row>
-    <row r="13" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="37">
         <v>12</v>
       </c>
       <c r="B13" s="34" t="s">
+        <v>125</v>
+      </c>
+      <c r="C13" s="35" t="s">
+        <v>147</v>
+      </c>
+      <c r="D13" s="41" t="s">
         <v>126</v>
       </c>
-      <c r="C13" s="35" t="s">
-        <v>149</v>
-      </c>
-      <c r="D13" s="41" t="s">
-        <v>127</v>
-      </c>
       <c r="E13" s="41" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F13" s="41" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G13" s="34" t="s">
         <v>95</v>
@@ -8192,28 +8108,28 @@
         <v>75</v>
       </c>
       <c r="N13" s="42" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O13" s="64"/>
     </row>
-    <row r="14" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="39">
         <v>13</v>
       </c>
       <c r="B14" s="35" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C14" s="34" t="s">
         <v>54</v>
       </c>
       <c r="D14" s="41" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E14" s="34" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F14" s="41" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G14" s="34" t="s">
         <v>55</v>
@@ -8237,28 +8153,28 @@
         <v>45453</v>
       </c>
       <c r="N14" s="42" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O14" s="64"/>
     </row>
-    <row r="15" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="37">
         <v>14</v>
       </c>
       <c r="B15" s="34" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C15" s="34" t="s">
         <v>99</v>
       </c>
       <c r="D15" s="41" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E15" s="34" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F15" s="41" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G15" s="34" t="s">
         <v>100</v>
@@ -8282,28 +8198,28 @@
         <v>45874</v>
       </c>
       <c r="N15" s="42" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="O15" s="64"/>
     </row>
-    <row r="16" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="39">
         <v>15</v>
       </c>
       <c r="B16" s="35" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C16" s="34" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D16" s="41" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E16" s="34" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F16" s="41" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G16" s="34" t="s">
         <v>103</v>
@@ -8327,11 +8243,11 @@
         <v>98</v>
       </c>
       <c r="N16" s="42" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O16" s="64"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="64"/>
       <c r="B17" s="64"/>
       <c r="C17" s="64"/>
@@ -8357,15 +8273,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCC9CB67-069E-4DDA-927B-C96C93506AB7}">
   <dimension ref="A1:P19"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.83203125" style="70" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.77734375" style="70" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="30.33203125" style="70" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.1640625" style="70" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.109375" style="70" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" style="70" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.83203125" style="70" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.77734375" style="70" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.6640625" style="70" customWidth="1"/>
-    <col min="7" max="7" width="25.5" style="70" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.44140625" style="70" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="31.6640625" style="70" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="4.6640625" style="70" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="22" style="70" bestFit="1" customWidth="1"/>
@@ -8377,24 +8293,24 @@
     <col min="16" max="16384" width="9.33203125" style="70"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="49" t="s">
+        <v>133</v>
+      </c>
+      <c r="B1" s="88" t="s">
+        <v>167</v>
+      </c>
+      <c r="C1" s="62" t="s">
+        <v>106</v>
+      </c>
+      <c r="D1" s="51" t="s">
+        <v>127</v>
+      </c>
+      <c r="E1" s="75" t="s">
+        <v>149</v>
+      </c>
+      <c r="F1" s="52" t="s">
         <v>134</v>
-      </c>
-      <c r="B1" s="50" t="s">
-        <v>135</v>
-      </c>
-      <c r="C1" s="62" t="s">
-        <v>107</v>
-      </c>
-      <c r="D1" s="51" t="s">
-        <v>128</v>
-      </c>
-      <c r="E1" s="75" t="s">
-        <v>151</v>
-      </c>
-      <c r="F1" s="52" t="s">
-        <v>136</v>
       </c>
       <c r="G1" s="52" t="s">
         <v>2</v>
@@ -8403,51 +8319,51 @@
         <v>3</v>
       </c>
       <c r="I1" s="53" t="s">
+        <v>135</v>
+      </c>
+      <c r="J1" s="52" t="s">
+        <v>136</v>
+      </c>
+      <c r="K1" s="76" t="s">
         <v>137</v>
       </c>
-      <c r="J1" s="52" t="s">
+      <c r="L1" s="49" t="s">
         <v>138</v>
       </c>
-      <c r="K1" s="76" t="s">
+      <c r="M1" s="76" t="s">
         <v>139</v>
-      </c>
-      <c r="L1" s="49" t="s">
-        <v>140</v>
-      </c>
-      <c r="M1" s="76" t="s">
-        <v>141</v>
       </c>
       <c r="N1" s="52" t="s">
         <v>8</v>
       </c>
       <c r="O1" s="18" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="67">
         <v>1</v>
       </c>
       <c r="B2" s="54" t="s">
+        <v>108</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="D2" s="33" t="s">
+        <v>126</v>
+      </c>
+      <c r="E2" s="33" t="s">
+        <v>158</v>
+      </c>
+      <c r="F2" s="55" t="s">
         <v>109</v>
       </c>
-      <c r="C2" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="D2" s="33" t="s">
-        <v>127</v>
-      </c>
-      <c r="E2" s="33" t="s">
-        <v>160</v>
-      </c>
-      <c r="F2" s="55" t="s">
-        <v>110</v>
-      </c>
       <c r="G2" s="11" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="H2" s="33" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I2" s="46">
         <v>1</v>
@@ -8465,35 +8381,35 @@
         <v>45405</v>
       </c>
       <c r="N2" s="17" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O2" s="68"/>
       <c r="P2" s="69"/>
     </row>
-    <row r="3" spans="1:16" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="71">
         <v>2</v>
       </c>
       <c r="B3" s="54" t="s">
+        <v>108</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="D3" s="33" t="s">
+        <v>126</v>
+      </c>
+      <c r="E3" s="33" t="s">
+        <v>158</v>
+      </c>
+      <c r="F3" s="55" t="s">
         <v>109</v>
       </c>
-      <c r="C3" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="D3" s="33" t="s">
-        <v>127</v>
-      </c>
-      <c r="E3" s="33" t="s">
-        <v>160</v>
-      </c>
-      <c r="F3" s="55" t="s">
-        <v>110</v>
-      </c>
       <c r="G3" s="11" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="H3" s="33" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="I3" s="46">
         <v>1</v>
@@ -8516,36 +8432,36 @@
       <c r="O3" s="68"/>
       <c r="P3" s="69"/>
     </row>
-    <row r="4" spans="1:16" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="71">
         <v>2</v>
       </c>
       <c r="B4" s="54" t="s">
+        <v>108</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="D4" s="33" t="s">
+        <v>126</v>
+      </c>
+      <c r="E4" s="33" t="s">
+        <v>158</v>
+      </c>
+      <c r="F4" s="55" t="s">
         <v>109</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="G4" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="D4" s="33" t="s">
-        <v>127</v>
-      </c>
-      <c r="E4" s="33" t="s">
-        <v>160</v>
-      </c>
-      <c r="F4" s="55" t="s">
-        <v>110</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>156</v>
-      </c>
       <c r="H4" s="33" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="I4" s="46">
         <v>1</v>
       </c>
       <c r="J4" s="17" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="K4" s="81">
         <v>45752</v>
@@ -8558,36 +8474,36 @@
       <c r="O4" s="68"/>
       <c r="P4" s="69"/>
     </row>
-    <row r="5" spans="1:16" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="71">
         <v>2</v>
       </c>
       <c r="B5" s="54" t="s">
+        <v>108</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="D5" s="33" t="s">
+        <v>126</v>
+      </c>
+      <c r="E5" s="33" t="s">
+        <v>158</v>
+      </c>
+      <c r="F5" s="55" t="s">
         <v>109</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="G5" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="D5" s="33" t="s">
-        <v>127</v>
-      </c>
-      <c r="E5" s="33" t="s">
-        <v>160</v>
-      </c>
-      <c r="F5" s="55" t="s">
-        <v>110</v>
-      </c>
-      <c r="G5" s="11" t="s">
-        <v>157</v>
-      </c>
       <c r="H5" s="33" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="I5" s="46">
         <v>1</v>
       </c>
       <c r="J5" s="17" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="K5" s="81">
         <v>45295</v>
@@ -8604,7 +8520,7 @@
       <c r="O5" s="68"/>
       <c r="P5" s="69"/>
     </row>
-    <row r="6" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="56">
         <v>3</v>
       </c>
@@ -8612,19 +8528,19 @@
         <v>40</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D6" s="33" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F6" s="55" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="H6" s="11" t="s">
         <v>41</v>
@@ -8645,12 +8561,12 @@
         <v>45921</v>
       </c>
       <c r="N6" s="17" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O6" s="68"/>
       <c r="P6" s="69"/>
     </row>
-    <row r="7" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="57">
         <v>4</v>
       </c>
@@ -8661,13 +8577,13 @@
         <v>47</v>
       </c>
       <c r="D7" s="33" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F7" s="55" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G7" s="16">
         <v>2920.0019080000002</v>
@@ -8691,35 +8607,35 @@
         <v>50</v>
       </c>
       <c r="N7" s="17" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O7" s="72"/>
       <c r="P7" s="73"/>
     </row>
-    <row r="8" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="59">
         <v>5</v>
       </c>
       <c r="B8" s="54" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>43</v>
       </c>
       <c r="D8" s="33" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F8" s="55" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G8" s="11" t="s">
         <v>44</v>
       </c>
       <c r="H8" s="33" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="I8" s="48">
         <v>1</v>
@@ -8737,12 +8653,12 @@
         <v>45404</v>
       </c>
       <c r="N8" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O8" s="72"/>
       <c r="P8" s="73"/>
     </row>
-    <row r="9" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="39"/>
       <c r="B9" s="34"/>
       <c r="C9" s="34"/>
@@ -8759,7 +8675,7 @@
       <c r="N9" s="42"/>
       <c r="O9" s="64"/>
     </row>
-    <row r="10" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="37"/>
       <c r="B10" s="35"/>
       <c r="C10" s="34"/>
@@ -8776,7 +8692,7 @@
       <c r="N10" s="42"/>
       <c r="O10" s="64"/>
     </row>
-    <row r="11" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="36"/>
       <c r="B11" s="35"/>
       <c r="C11" s="34"/>
@@ -8793,7 +8709,7 @@
       <c r="N11" s="42"/>
       <c r="O11" s="64"/>
     </row>
-    <row r="12" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="37"/>
       <c r="B12" s="35"/>
       <c r="C12" s="34"/>
@@ -8810,7 +8726,7 @@
       <c r="N12" s="42"/>
       <c r="O12" s="64"/>
     </row>
-    <row r="13" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="37"/>
       <c r="B13" s="34"/>
       <c r="C13" s="34"/>
@@ -8827,7 +8743,7 @@
       <c r="N13" s="42"/>
       <c r="O13" s="64"/>
     </row>
-    <row r="14" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="34"/>
       <c r="B14" s="34"/>
       <c r="C14" s="40"/>
@@ -8844,7 +8760,7 @@
       <c r="N14" s="42"/>
       <c r="O14" s="64"/>
     </row>
-    <row r="15" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="36"/>
       <c r="B15" s="34"/>
       <c r="C15" s="35"/>
@@ -8861,7 +8777,7 @@
       <c r="N15" s="42"/>
       <c r="O15" s="64"/>
     </row>
-    <row r="16" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="39"/>
       <c r="B16" s="35"/>
       <c r="C16" s="34"/>
@@ -8878,7 +8794,7 @@
       <c r="N16" s="42"/>
       <c r="O16" s="64"/>
     </row>
-    <row r="17" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="36"/>
       <c r="B17" s="34"/>
       <c r="C17" s="34"/>
@@ -8895,7 +8811,7 @@
       <c r="N17" s="42"/>
       <c r="O17" s="64"/>
     </row>
-    <row r="18" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="37"/>
       <c r="B18" s="35"/>
       <c r="C18" s="34"/>
@@ -8912,7 +8828,7 @@
       <c r="N18" s="42"/>
       <c r="O18" s="64"/>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="64"/>
       <c r="B19" s="64"/>
       <c r="C19" s="64"/>

--- a/data/FRS_cleaned/Nov/Fmn D Nov/WorkOrderRemote_Nov 2025 D.xlsx
+++ b/data/FRS_cleaned/Nov/Fmn D Nov/WorkOrderRemote_Nov 2025 D.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Anu\APT\apt\army\fortwilliam\code\fwDemo\data\FRS_cleaned\Nov\Fmn D Nov\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{009EB9EF-2D17-4F68-92B9-63ACE4C9AAF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFA2E7DC-4BEB-42D0-98B3-EA1CBD3F9A3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30" yWindow="-16170" windowWidth="28800" windowHeight="15195" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Eng" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="166">
   <si>
     <r>
       <rPr>
@@ -4952,58 +4952,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>HI</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF363836"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
       <t>H1</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>F</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF363836"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>l</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1D1F1D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>H</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF030503"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>I</t>
     </r>
   </si>
   <si>
@@ -6366,6 +6315,9 @@
   </si>
   <si>
     <t>Category</t>
+  </si>
+  <si>
+    <t>H1</t>
   </si>
 </sst>
 </file>
@@ -6666,7 +6618,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -6933,6 +6885,12 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -7259,16 +7217,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="29" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C1" s="30" t="s">
         <v>106</v>
       </c>
       <c r="D1" s="31" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E1" s="74" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F1" s="21" t="s">
         <v>1</v>
@@ -7312,10 +7270,10 @@
         <v>9</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F2" s="22" t="s">
         <v>109</v>
@@ -7359,10 +7317,10 @@
         <v>18</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F3" s="22" t="s">
         <v>109</v>
@@ -7406,10 +7364,10 @@
         <v>26</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E4" s="21" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F4" s="22" t="s">
         <v>109</v>
@@ -7447,16 +7405,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="32" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C5" s="24" t="s">
         <v>31</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F5" s="22" t="s">
         <v>109</v>
@@ -7519,22 +7477,22 @@
   <sheetData>
     <row r="1" spans="1:15" s="63" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="49" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B1" s="50" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C1" s="62" t="s">
         <v>106</v>
       </c>
       <c r="D1" s="51" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E1" s="75" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F1" s="52" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="G1" s="52" t="s">
         <v>2</v>
@@ -7543,19 +7501,19 @@
         <v>3</v>
       </c>
       <c r="I1" s="53" t="s">
+        <v>132</v>
+      </c>
+      <c r="J1" s="52" t="s">
+        <v>133</v>
+      </c>
+      <c r="K1" s="76" t="s">
+        <v>134</v>
+      </c>
+      <c r="L1" s="49" t="s">
         <v>135</v>
       </c>
-      <c r="J1" s="52" t="s">
+      <c r="M1" s="76" t="s">
         <v>136</v>
-      </c>
-      <c r="K1" s="76" t="s">
-        <v>137</v>
-      </c>
-      <c r="L1" s="49" t="s">
-        <v>138</v>
-      </c>
-      <c r="M1" s="76" t="s">
-        <v>139</v>
       </c>
       <c r="N1" s="52" t="s">
         <v>8</v>
@@ -7569,16 +7527,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="35" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C2" s="34" t="s">
         <v>51</v>
       </c>
       <c r="D2" s="41" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E2" s="34" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="F2" s="41" t="s">
         <v>109</v>
@@ -7587,7 +7545,7 @@
         <v>52</v>
       </c>
       <c r="H2" s="44" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="I2" s="39">
         <v>1</v>
@@ -7608,7 +7566,7 @@
         <v>113</v>
       </c>
       <c r="O2" s="64" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -7622,10 +7580,10 @@
         <v>62</v>
       </c>
       <c r="D3" s="41" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E3" s="41" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F3" s="41" t="s">
         <v>109</v>
@@ -7652,7 +7610,7 @@
         <v>45453</v>
       </c>
       <c r="N3" s="42" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="O3" s="64"/>
     </row>
@@ -7667,16 +7625,16 @@
         <v>67</v>
       </c>
       <c r="D4" s="41" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E4" s="34" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F4" s="41" t="s">
         <v>109</v>
       </c>
       <c r="G4" s="44" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="H4" s="34" t="s">
         <v>68</v>
@@ -7685,7 +7643,7 @@
         <v>1</v>
       </c>
       <c r="J4" s="45" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="K4" s="78">
         <v>45593</v>
@@ -7697,7 +7655,7 @@
         <v>45609</v>
       </c>
       <c r="N4" s="42" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="O4" s="64" t="s">
         <v>114</v>
@@ -7711,13 +7669,13 @@
         <v>69</v>
       </c>
       <c r="C5" s="44" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D5" s="41" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E5" s="34" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F5" s="41" t="s">
         <v>109</v>
@@ -7747,7 +7705,7 @@
         <v>113</v>
       </c>
       <c r="O5" s="64" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -7761,10 +7719,10 @@
         <v>58</v>
       </c>
       <c r="D6" s="41" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E6" s="34" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="F6" s="41" t="s">
         <v>109</v>
@@ -7791,7 +7749,7 @@
         <v>45453</v>
       </c>
       <c r="N6" s="42" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="O6" s="64"/>
     </row>
@@ -7806,19 +7764,19 @@
         <v>73</v>
       </c>
       <c r="D7" s="41" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E7" s="34" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F7" s="41" t="s">
         <v>109</v>
       </c>
       <c r="G7" s="34" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="H7" s="44" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="I7" s="36">
         <v>1</v>
@@ -7845,16 +7803,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="35" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C8" s="34" t="s">
         <v>76</v>
       </c>
       <c r="D8" s="41" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E8" s="34" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F8" s="41" t="s">
         <v>109</v>
@@ -7881,7 +7839,7 @@
         <v>75</v>
       </c>
       <c r="N8" s="42" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="O8" s="64"/>
     </row>
@@ -7890,22 +7848,22 @@
         <v>8</v>
       </c>
       <c r="B9" s="35" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="C9" s="34" t="s">
         <v>81</v>
       </c>
       <c r="D9" s="41" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F9" s="41" t="s">
         <v>109</v>
       </c>
       <c r="G9" s="34" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="H9" s="34" t="s">
         <v>82</v>
@@ -7926,7 +7884,7 @@
         <v>45717</v>
       </c>
       <c r="N9" s="42" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="O9" s="64"/>
     </row>
@@ -7935,16 +7893,16 @@
         <v>9</v>
       </c>
       <c r="B10" s="35" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C10" s="34" t="s">
         <v>84</v>
       </c>
       <c r="D10" s="41" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E10" s="41" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="F10" s="41" t="s">
         <v>109</v>
@@ -7971,10 +7929,10 @@
         <v>45717</v>
       </c>
       <c r="N10" s="42" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="O10" s="64" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -7982,22 +7940,22 @@
         <v>10</v>
       </c>
       <c r="B11" s="34" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C11" s="34" t="s">
         <v>88</v>
       </c>
       <c r="D11" s="41" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E11" s="34" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F11" s="41" t="s">
         <v>109</v>
       </c>
       <c r="G11" s="34" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="H11" s="34" t="s">
         <v>89</v>
@@ -8018,7 +7976,7 @@
         <v>45719</v>
       </c>
       <c r="N11" s="42" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="O11" s="64"/>
     </row>
@@ -8027,16 +7985,16 @@
         <v>11</v>
       </c>
       <c r="B12" s="34" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C12" s="34" t="s">
         <v>91</v>
       </c>
       <c r="D12" s="41" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E12" s="34" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F12" s="41" t="s">
         <v>109</v>
@@ -8063,7 +8021,7 @@
         <v>45735</v>
       </c>
       <c r="N12" s="42" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="O12" s="64"/>
     </row>
@@ -8072,16 +8030,16 @@
         <v>12</v>
       </c>
       <c r="B13" s="34" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C13" s="35" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D13" s="41" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E13" s="41" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="F13" s="41" t="s">
         <v>109</v>
@@ -8108,7 +8066,7 @@
         <v>75</v>
       </c>
       <c r="N13" s="42" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="O13" s="64"/>
     </row>
@@ -8117,16 +8075,16 @@
         <v>13</v>
       </c>
       <c r="B14" s="35" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C14" s="34" t="s">
         <v>54</v>
       </c>
       <c r="D14" s="41" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E14" s="34" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F14" s="41" t="s">
         <v>109</v>
@@ -8153,7 +8111,7 @@
         <v>45453</v>
       </c>
       <c r="N14" s="42" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="O14" s="64"/>
     </row>
@@ -8162,16 +8120,16 @@
         <v>14</v>
       </c>
       <c r="B15" s="34" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C15" s="34" t="s">
         <v>99</v>
       </c>
       <c r="D15" s="41" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E15" s="34" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F15" s="41" t="s">
         <v>109</v>
@@ -8207,16 +8165,16 @@
         <v>15</v>
       </c>
       <c r="B16" s="35" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C16" s="34" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D16" s="41" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E16" s="34" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F16" s="41" t="s">
         <v>109</v>
@@ -8243,7 +8201,7 @@
         <v>98</v>
       </c>
       <c r="N16" s="42" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="O16" s="64"/>
     </row>
@@ -8295,22 +8253,22 @@
   <sheetData>
     <row r="1" spans="1:16" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="49" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B1" s="88" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C1" s="62" t="s">
         <v>106</v>
       </c>
       <c r="D1" s="51" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E1" s="75" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F1" s="52" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="G1" s="52" t="s">
         <v>2</v>
@@ -8319,19 +8277,19 @@
         <v>3</v>
       </c>
       <c r="I1" s="53" t="s">
+        <v>132</v>
+      </c>
+      <c r="J1" s="52" t="s">
+        <v>133</v>
+      </c>
+      <c r="K1" s="76" t="s">
+        <v>134</v>
+      </c>
+      <c r="L1" s="49" t="s">
         <v>135</v>
       </c>
-      <c r="J1" s="52" t="s">
+      <c r="M1" s="76" t="s">
         <v>136</v>
-      </c>
-      <c r="K1" s="76" t="s">
-        <v>137</v>
-      </c>
-      <c r="L1" s="49" t="s">
-        <v>138</v>
-      </c>
-      <c r="M1" s="76" t="s">
-        <v>139</v>
       </c>
       <c r="N1" s="52" t="s">
         <v>8</v>
@@ -8351,16 +8309,16 @@
         <v>110</v>
       </c>
       <c r="D2" s="33" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E2" s="33" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F2" s="55" t="s">
         <v>109</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="H2" s="33" t="s">
         <v>112</v>
@@ -8380,8 +8338,8 @@
       <c r="M2" s="77">
         <v>45405</v>
       </c>
-      <c r="N2" s="17" t="s">
-        <v>116</v>
+      <c r="N2" s="90" t="s">
+        <v>165</v>
       </c>
       <c r="O2" s="68"/>
       <c r="P2" s="69"/>
@@ -8394,22 +8352,22 @@
         <v>108</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D3" s="33" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E3" s="33" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F3" s="55" t="s">
         <v>109</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="H3" s="33" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I3" s="46">
         <v>1</v>
@@ -8440,28 +8398,28 @@
         <v>108</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D4" s="33" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E4" s="33" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F4" s="55" t="s">
         <v>109</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="H4" s="33" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I4" s="46">
         <v>1</v>
       </c>
       <c r="J4" s="17" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="K4" s="81">
         <v>45752</v>
@@ -8482,28 +8440,28 @@
         <v>108</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D5" s="33" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F5" s="55" t="s">
         <v>109</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="H5" s="33" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I5" s="46">
         <v>1</v>
       </c>
       <c r="J5" s="17" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="K5" s="81">
         <v>45295</v>
@@ -8531,16 +8489,16 @@
         <v>111</v>
       </c>
       <c r="D6" s="33" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F6" s="55" t="s">
         <v>109</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="H6" s="11" t="s">
         <v>41</v>
@@ -8561,7 +8519,7 @@
         <v>45921</v>
       </c>
       <c r="N6" s="17" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O6" s="68"/>
       <c r="P6" s="69"/>
@@ -8577,10 +8535,10 @@
         <v>47</v>
       </c>
       <c r="D7" s="33" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F7" s="55" t="s">
         <v>109</v>
@@ -8606,8 +8564,8 @@
       <c r="M7" s="77" t="s">
         <v>50</v>
       </c>
-      <c r="N7" s="17" t="s">
-        <v>119</v>
+      <c r="N7" s="89" t="s">
+        <v>165</v>
       </c>
       <c r="O7" s="72"/>
       <c r="P7" s="73"/>
@@ -8617,16 +8575,16 @@
         <v>5</v>
       </c>
       <c r="B8" s="54" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>43</v>
       </c>
       <c r="D8" s="33" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="F8" s="55" t="s">
         <v>109</v>
@@ -8635,7 +8593,7 @@
         <v>44</v>
       </c>
       <c r="H8" s="33" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="I8" s="48">
         <v>1</v>
@@ -8652,8 +8610,8 @@
       <c r="M8" s="77">
         <v>45404</v>
       </c>
-      <c r="N8" s="17" t="s">
-        <v>118</v>
+      <c r="N8" s="89" t="s">
+        <v>113</v>
       </c>
       <c r="O8" s="72"/>
       <c r="P8" s="73"/>

--- a/data/FRS_cleaned/Nov/Fmn D Nov/WorkOrderRemote_Nov 2025 D.xlsx
+++ b/data/FRS_cleaned/Nov/Fmn D Nov/WorkOrderRemote_Nov 2025 D.xlsx
@@ -8,21 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Anu\APT\apt\army\fortwilliam\code\fwDemo\data\FRS_cleaned\Nov\Fmn D Nov\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFA2E7DC-4BEB-42D0-98B3-EA1CBD3F9A3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{474D8DEC-A9B9-438A-9F29-35A997538B06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1080" yWindow="-14745" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Eng" sheetId="2" r:id="rId1"/>
     <sheet name="EOA Spares" sheetId="3" r:id="rId2"/>
-    <sheet name="MUA" sheetId="4" r:id="rId3"/>
+    <sheet name="VOR Spares" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="165">
   <si>
     <r>
       <rPr>
@@ -634,37 +634,6 @@
         <family val="2"/>
       </rPr>
       <t>26</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1C1D1C"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>NVR</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1C1D1C"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF363634"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>VR</t>
     </r>
   </si>
   <si>
@@ -6318,6 +6287,9 @@
   </si>
   <si>
     <t>H1</t>
+  </si>
+  <si>
+    <t>NYR</t>
   </si>
 </sst>
 </file>
@@ -6632,9 +6604,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -6871,9 +6840,6 @@
     <xf numFmtId="165" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
-    </xf>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -6891,6 +6857,12 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -7206,77 +7178,77 @@
     <col min="7" max="7" width="25.33203125" customWidth="1"/>
     <col min="8" max="8" width="50.44140625" customWidth="1"/>
     <col min="10" max="10" width="22.77734375" customWidth="1"/>
-    <col min="11" max="11" width="14.109375" style="86" customWidth="1"/>
+    <col min="11" max="11" width="14.109375" style="84" customWidth="1"/>
     <col min="12" max="12" width="14.77734375" customWidth="1"/>
-    <col min="13" max="13" width="14.33203125" style="86" customWidth="1"/>
+    <col min="13" max="13" width="14.33203125" style="84" customWidth="1"/>
     <col min="15" max="15" width="46.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="29" t="s">
-        <v>164</v>
-      </c>
-      <c r="C1" s="30" t="s">
-        <v>106</v>
-      </c>
-      <c r="D1" s="31" t="s">
-        <v>124</v>
-      </c>
-      <c r="E1" s="74" t="s">
-        <v>146</v>
-      </c>
-      <c r="F1" s="21" t="s">
+      <c r="B1" s="28" t="s">
+        <v>162</v>
+      </c>
+      <c r="C1" s="29" t="s">
+        <v>104</v>
+      </c>
+      <c r="D1" s="30" t="s">
+        <v>122</v>
+      </c>
+      <c r="E1" s="73" t="s">
+        <v>144</v>
+      </c>
+      <c r="F1" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="26" t="s">
+      <c r="G1" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="26" t="s">
+      <c r="H1" s="25" t="s">
         <v>3</v>
       </c>
       <c r="I1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="21" t="s">
+      <c r="J1" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="83" t="s">
+      <c r="K1" s="82" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="25" t="s">
+      <c r="L1" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="M1" s="83" t="s">
-        <v>115</v>
-      </c>
-      <c r="N1" s="26" t="s">
+      <c r="M1" s="82" t="s">
+        <v>113</v>
+      </c>
+      <c r="N1" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="O1" s="18" t="s">
-        <v>107</v>
+      <c r="O1" s="17" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:15" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="19">
+      <c r="A2" s="18">
         <v>1</v>
       </c>
-      <c r="B2" s="20" t="s">
-        <v>108</v>
-      </c>
-      <c r="C2" s="25" t="s">
+      <c r="B2" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="C2" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="21" t="s">
-        <v>123</v>
-      </c>
-      <c r="E2" s="21" t="s">
-        <v>155</v>
-      </c>
-      <c r="F2" s="22" t="s">
-        <v>109</v>
+      <c r="D2" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="E2" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="F2" s="21" t="s">
+        <v>107</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>10</v>
@@ -7284,167 +7256,167 @@
       <c r="H2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="11">
         <v>1</v>
       </c>
-      <c r="J2" s="23" t="s">
+      <c r="J2" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="K2" s="87">
+      <c r="K2" s="85">
         <v>45578</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="90" t="s">
+        <v>164</v>
+      </c>
+      <c r="M2" s="89" t="s">
+        <v>164</v>
+      </c>
+      <c r="N2" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="M2" s="84" t="s">
+      <c r="O2" s="4" t="s">
         <v>14</v>
-      </c>
-      <c r="N2" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="O2" s="5" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:15" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="27">
+      <c r="A3" s="26">
         <v>2</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="G3" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="H3" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="21" t="s">
-        <v>123</v>
-      </c>
-      <c r="E3" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="F3" s="22" t="s">
-        <v>109</v>
-      </c>
-      <c r="G3" s="11" t="s">
+      <c r="I3" s="13">
+        <v>1</v>
+      </c>
+      <c r="J3" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="K3" s="85">
+        <v>45943</v>
+      </c>
+      <c r="L3" s="6">
+        <v>251017983</v>
+      </c>
+      <c r="M3" s="83">
+        <v>45988</v>
+      </c>
+      <c r="N3" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="14">
-        <v>1</v>
-      </c>
-      <c r="J3" s="23" t="s">
+      <c r="O3" s="5" t="s">
         <v>21</v>
-      </c>
-      <c r="K3" s="87">
-        <v>45943</v>
-      </c>
-      <c r="L3" s="7">
-        <v>251017983</v>
-      </c>
-      <c r="M3" s="85">
-        <v>45988</v>
-      </c>
-      <c r="N3" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="O3" s="6" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:15" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="28">
+      <c r="A4" s="27">
         <v>3</v>
       </c>
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="F4" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="G4" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="24" t="s">
+      <c r="H4" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="21" t="s">
-        <v>123</v>
-      </c>
-      <c r="E4" s="21" t="s">
-        <v>158</v>
-      </c>
-      <c r="F4" s="22" t="s">
-        <v>109</v>
-      </c>
-      <c r="G4" s="11" t="s">
+      <c r="I4" s="12">
+        <v>1</v>
+      </c>
+      <c r="J4" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="K4" s="85">
+        <v>45959</v>
+      </c>
+      <c r="L4" s="9">
+        <v>251018435</v>
+      </c>
+      <c r="M4" s="83">
+        <v>45988</v>
+      </c>
+      <c r="N4" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="O4" s="8" t="s">
         <v>28</v>
-      </c>
-      <c r="I4" s="13">
-        <v>1</v>
-      </c>
-      <c r="J4" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="K4" s="87">
-        <v>45959</v>
-      </c>
-      <c r="L4" s="10">
-        <v>251018435</v>
-      </c>
-      <c r="M4" s="85">
-        <v>45988</v>
-      </c>
-      <c r="N4" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="O4" s="9" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:15" s="1" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="28">
+      <c r="A5" s="27">
         <v>4</v>
       </c>
-      <c r="B5" s="32" t="s">
-        <v>125</v>
-      </c>
-      <c r="C5" s="24" t="s">
+      <c r="B5" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="C5" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="F5" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="D5" s="21" t="s">
-        <v>123</v>
-      </c>
-      <c r="E5" s="21" t="s">
-        <v>158</v>
-      </c>
-      <c r="F5" s="22" t="s">
-        <v>109</v>
-      </c>
-      <c r="G5" s="11" t="s">
+      <c r="I5" s="13">
+        <v>1</v>
+      </c>
+      <c r="J5" s="22" t="s">
         <v>32</v>
       </c>
-      <c r="H5" s="11" t="s">
+      <c r="K5" s="85">
+        <v>45961</v>
+      </c>
+      <c r="L5" s="9">
+        <v>251017997</v>
+      </c>
+      <c r="M5" s="83">
+        <v>45988</v>
+      </c>
+      <c r="N5" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="O5" s="5" t="s">
         <v>33</v>
-      </c>
-      <c r="I5" s="14">
-        <v>1</v>
-      </c>
-      <c r="J5" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="K5" s="87">
-        <v>45961</v>
-      </c>
-      <c r="L5" s="10">
-        <v>251017997</v>
-      </c>
-      <c r="M5" s="85">
-        <v>45988</v>
-      </c>
-      <c r="N5" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="O5" s="6" t="s">
-        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -7457,770 +7429,770 @@
   <dimension ref="A1:O17"/>
   <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.33203125" style="65"/>
-    <col min="2" max="2" width="14" style="65" customWidth="1"/>
-    <col min="3" max="3" width="19.44140625" style="65" customWidth="1"/>
-    <col min="4" max="4" width="13.77734375" style="65" customWidth="1"/>
-    <col min="5" max="5" width="15.6640625" style="65" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.6640625" style="65" customWidth="1"/>
-    <col min="7" max="7" width="32.6640625" style="65" customWidth="1"/>
-    <col min="8" max="8" width="44.44140625" style="65" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.33203125" style="65"/>
-    <col min="10" max="10" width="33.33203125" style="65" customWidth="1"/>
-    <col min="11" max="11" width="14" style="82" customWidth="1"/>
-    <col min="12" max="12" width="15.6640625" style="65" customWidth="1"/>
-    <col min="13" max="13" width="14.77734375" style="82" customWidth="1"/>
-    <col min="14" max="14" width="9.33203125" style="65"/>
-    <col min="15" max="15" width="60.109375" style="65" customWidth="1"/>
-    <col min="16" max="16384" width="9.33203125" style="65"/>
+    <col min="1" max="1" width="9.33203125" style="64"/>
+    <col min="2" max="2" width="14" style="64" customWidth="1"/>
+    <col min="3" max="3" width="19.44140625" style="64" customWidth="1"/>
+    <col min="4" max="4" width="13.77734375" style="64" customWidth="1"/>
+    <col min="5" max="5" width="15.6640625" style="64" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" style="64" customWidth="1"/>
+    <col min="7" max="7" width="32.6640625" style="64" customWidth="1"/>
+    <col min="8" max="8" width="44.44140625" style="64" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.33203125" style="64"/>
+    <col min="10" max="10" width="33.33203125" style="64" customWidth="1"/>
+    <col min="11" max="11" width="14" style="81" customWidth="1"/>
+    <col min="12" max="12" width="15.6640625" style="64" customWidth="1"/>
+    <col min="13" max="13" width="14.77734375" style="81" customWidth="1"/>
+    <col min="14" max="14" width="9.33203125" style="64"/>
+    <col min="15" max="15" width="60.109375" style="64" customWidth="1"/>
+    <col min="16" max="16384" width="9.33203125" style="64"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="63" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="49" t="s">
+    <row r="1" spans="1:15" s="62" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="48" t="s">
+        <v>128</v>
+      </c>
+      <c r="B1" s="49" t="s">
+        <v>162</v>
+      </c>
+      <c r="C1" s="61" t="s">
+        <v>104</v>
+      </c>
+      <c r="D1" s="50" t="s">
+        <v>122</v>
+      </c>
+      <c r="E1" s="74" t="s">
+        <v>144</v>
+      </c>
+      <c r="F1" s="51" t="s">
+        <v>129</v>
+      </c>
+      <c r="G1" s="51" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="51" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" s="52" t="s">
         <v>130</v>
       </c>
-      <c r="B1" s="50" t="s">
-        <v>164</v>
-      </c>
-      <c r="C1" s="62" t="s">
-        <v>106</v>
-      </c>
-      <c r="D1" s="51" t="s">
-        <v>124</v>
-      </c>
-      <c r="E1" s="75" t="s">
-        <v>146</v>
-      </c>
-      <c r="F1" s="52" t="s">
+      <c r="J1" s="51" t="s">
         <v>131</v>
       </c>
-      <c r="G1" s="52" t="s">
-        <v>2</v>
-      </c>
-      <c r="H1" s="52" t="s">
-        <v>3</v>
-      </c>
-      <c r="I1" s="53" t="s">
+      <c r="K1" s="75" t="s">
         <v>132</v>
       </c>
-      <c r="J1" s="52" t="s">
+      <c r="L1" s="48" t="s">
         <v>133</v>
       </c>
-      <c r="K1" s="76" t="s">
+      <c r="M1" s="75" t="s">
         <v>134</v>
       </c>
-      <c r="L1" s="49" t="s">
-        <v>135</v>
-      </c>
-      <c r="M1" s="76" t="s">
-        <v>136</v>
-      </c>
-      <c r="N1" s="52" t="s">
+      <c r="N1" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="O1" s="61" t="s">
-        <v>107</v>
+      <c r="O1" s="60" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="39">
+      <c r="A2" s="38">
         <v>1</v>
       </c>
-      <c r="B2" s="35" t="s">
-        <v>126</v>
-      </c>
-      <c r="C2" s="34" t="s">
+      <c r="B2" s="34" t="s">
+        <v>124</v>
+      </c>
+      <c r="C2" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="40" t="s">
+        <v>121</v>
+      </c>
+      <c r="E2" s="33" t="s">
+        <v>145</v>
+      </c>
+      <c r="F2" s="40" t="s">
+        <v>107</v>
+      </c>
+      <c r="G2" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="H2" s="43" t="s">
+        <v>117</v>
+      </c>
+      <c r="I2" s="38">
+        <v>1</v>
+      </c>
+      <c r="J2" s="41" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="41" t="s">
-        <v>123</v>
-      </c>
-      <c r="E2" s="34" t="s">
-        <v>147</v>
-      </c>
-      <c r="F2" s="41" t="s">
-        <v>109</v>
-      </c>
-      <c r="G2" s="34" t="s">
-        <v>52</v>
-      </c>
-      <c r="H2" s="44" t="s">
-        <v>119</v>
-      </c>
-      <c r="I2" s="39">
-        <v>1</v>
-      </c>
-      <c r="J2" s="42" t="s">
-        <v>53</v>
-      </c>
-      <c r="K2" s="78">
+      <c r="K2" s="77">
         <v>45057</v>
       </c>
-      <c r="L2" s="43">
+      <c r="L2" s="42">
         <v>4503235454</v>
       </c>
-      <c r="M2" s="78">
+      <c r="M2" s="77">
         <v>45814</v>
       </c>
-      <c r="N2" s="42" t="s">
-        <v>113</v>
-      </c>
-      <c r="O2" s="64" t="s">
-        <v>145</v>
+      <c r="N2" s="41" t="s">
+        <v>111</v>
+      </c>
+      <c r="O2" s="63" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="37">
+      <c r="A3" s="36">
         <v>2</v>
       </c>
-      <c r="B3" s="35" t="s">
-        <v>108</v>
-      </c>
-      <c r="C3" s="34" t="s">
+      <c r="B3" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="C3" s="33" t="s">
+        <v>60</v>
+      </c>
+      <c r="D3" s="40" t="s">
+        <v>121</v>
+      </c>
+      <c r="E3" s="40" t="s">
+        <v>153</v>
+      </c>
+      <c r="F3" s="40" t="s">
+        <v>107</v>
+      </c>
+      <c r="G3" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="H3" s="33" t="s">
         <v>62</v>
       </c>
-      <c r="D3" s="41" t="s">
-        <v>123</v>
-      </c>
-      <c r="E3" s="41" t="s">
-        <v>155</v>
-      </c>
-      <c r="F3" s="41" t="s">
-        <v>109</v>
-      </c>
-      <c r="G3" s="34" t="s">
+      <c r="I3" s="36">
+        <v>1</v>
+      </c>
+      <c r="J3" s="41" t="s">
         <v>63</v>
       </c>
-      <c r="H3" s="34" t="s">
-        <v>64</v>
-      </c>
-      <c r="I3" s="37">
-        <v>1</v>
-      </c>
-      <c r="J3" s="42" t="s">
-        <v>65</v>
-      </c>
-      <c r="K3" s="78">
+      <c r="K3" s="77">
         <v>45432</v>
       </c>
-      <c r="L3" s="43">
+      <c r="L3" s="42">
         <v>241001945</v>
       </c>
-      <c r="M3" s="78">
+      <c r="M3" s="77">
         <v>45453</v>
       </c>
-      <c r="N3" s="42" t="s">
-        <v>118</v>
-      </c>
-      <c r="O3" s="64"/>
+      <c r="N3" s="41" t="s">
+        <v>116</v>
+      </c>
+      <c r="O3" s="63"/>
     </row>
     <row r="4" spans="1:15" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="39">
+      <c r="A4" s="38">
         <v>3</v>
       </c>
-      <c r="B4" s="34" t="s">
+      <c r="B4" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4" s="33" t="s">
+        <v>65</v>
+      </c>
+      <c r="D4" s="40" t="s">
+        <v>121</v>
+      </c>
+      <c r="E4" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="F4" s="40" t="s">
+        <v>107</v>
+      </c>
+      <c r="G4" s="43" t="s">
+        <v>161</v>
+      </c>
+      <c r="H4" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="C4" s="34" t="s">
-        <v>67</v>
-      </c>
-      <c r="D4" s="41" t="s">
-        <v>123</v>
-      </c>
-      <c r="E4" s="34" t="s">
-        <v>155</v>
-      </c>
-      <c r="F4" s="41" t="s">
-        <v>109</v>
-      </c>
-      <c r="G4" s="44" t="s">
-        <v>163</v>
-      </c>
-      <c r="H4" s="34" t="s">
-        <v>68</v>
-      </c>
-      <c r="I4" s="37">
+      <c r="I4" s="36">
         <v>1</v>
       </c>
-      <c r="J4" s="45" t="s">
-        <v>137</v>
-      </c>
-      <c r="K4" s="78">
+      <c r="J4" s="44" t="s">
+        <v>135</v>
+      </c>
+      <c r="K4" s="77">
         <v>45593</v>
       </c>
-      <c r="L4" s="38">
+      <c r="L4" s="37">
         <v>243001650</v>
       </c>
-      <c r="M4" s="78">
+      <c r="M4" s="77">
         <v>45609</v>
       </c>
-      <c r="N4" s="42" t="s">
-        <v>117</v>
-      </c>
-      <c r="O4" s="64" t="s">
-        <v>114</v>
+      <c r="N4" s="41" t="s">
+        <v>115</v>
+      </c>
+      <c r="O4" s="63" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="37">
+      <c r="A5" s="36">
         <v>4</v>
       </c>
-      <c r="B5" s="34" t="s">
+      <c r="B5" s="33" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" s="43" t="s">
+        <v>141</v>
+      </c>
+      <c r="D5" s="40" t="s">
+        <v>121</v>
+      </c>
+      <c r="E5" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="F5" s="40" t="s">
+        <v>107</v>
+      </c>
+      <c r="G5" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="H5" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="C5" s="44" t="s">
+      <c r="I5" s="36">
+        <v>1</v>
+      </c>
+      <c r="J5" s="41" t="s">
+        <v>70</v>
+      </c>
+      <c r="K5" s="77">
+        <v>45593</v>
+      </c>
+      <c r="L5" s="37">
+        <v>241010808</v>
+      </c>
+      <c r="M5" s="77">
+        <v>45609</v>
+      </c>
+      <c r="N5" s="41" t="s">
+        <v>111</v>
+      </c>
+      <c r="O5" s="63" t="s">
         <v>143</v>
-      </c>
-      <c r="D5" s="41" t="s">
-        <v>123</v>
-      </c>
-      <c r="E5" s="34" t="s">
-        <v>155</v>
-      </c>
-      <c r="F5" s="41" t="s">
-        <v>109</v>
-      </c>
-      <c r="G5" s="34" t="s">
-        <v>70</v>
-      </c>
-      <c r="H5" s="34" t="s">
-        <v>71</v>
-      </c>
-      <c r="I5" s="37">
-        <v>1</v>
-      </c>
-      <c r="J5" s="42" t="s">
-        <v>72</v>
-      </c>
-      <c r="K5" s="78">
-        <v>45593</v>
-      </c>
-      <c r="L5" s="38">
-        <v>241010808</v>
-      </c>
-      <c r="M5" s="78">
-        <v>45609</v>
-      </c>
-      <c r="N5" s="42" t="s">
-        <v>113</v>
-      </c>
-      <c r="O5" s="64" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="39">
+      <c r="A6" s="38">
         <v>5</v>
       </c>
-      <c r="B6" s="35" t="s">
-        <v>108</v>
-      </c>
-      <c r="C6" s="34" t="s">
+      <c r="B6" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="C6" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="D6" s="40" t="s">
+        <v>121</v>
+      </c>
+      <c r="E6" s="33" t="s">
+        <v>154</v>
+      </c>
+      <c r="F6" s="40" t="s">
+        <v>107</v>
+      </c>
+      <c r="G6" s="33" t="s">
+        <v>57</v>
+      </c>
+      <c r="H6" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="D6" s="41" t="s">
-        <v>123</v>
-      </c>
-      <c r="E6" s="34" t="s">
-        <v>156</v>
-      </c>
-      <c r="F6" s="41" t="s">
-        <v>109</v>
-      </c>
-      <c r="G6" s="34" t="s">
+      <c r="I6" s="35">
+        <v>1</v>
+      </c>
+      <c r="J6" s="41" t="s">
         <v>59</v>
       </c>
-      <c r="H6" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="I6" s="36">
-        <v>1</v>
-      </c>
-      <c r="J6" s="42" t="s">
-        <v>61</v>
-      </c>
-      <c r="K6" s="78">
+      <c r="K6" s="77">
         <v>45432</v>
       </c>
-      <c r="L6" s="43">
+      <c r="L6" s="42">
         <v>241001944</v>
       </c>
-      <c r="M6" s="78">
+      <c r="M6" s="77">
         <v>45453</v>
       </c>
-      <c r="N6" s="42" t="s">
-        <v>117</v>
-      </c>
-      <c r="O6" s="64"/>
+      <c r="N6" s="41" t="s">
+        <v>115</v>
+      </c>
+      <c r="O6" s="63"/>
     </row>
     <row r="7" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="37">
+      <c r="A7" s="36">
         <v>6</v>
       </c>
-      <c r="B7" s="34" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" s="34" t="s">
+      <c r="B7" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="33" t="s">
+        <v>71</v>
+      </c>
+      <c r="D7" s="40" t="s">
+        <v>121</v>
+      </c>
+      <c r="E7" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="F7" s="40" t="s">
+        <v>107</v>
+      </c>
+      <c r="G7" s="33" t="s">
+        <v>160</v>
+      </c>
+      <c r="H7" s="43" t="s">
+        <v>118</v>
+      </c>
+      <c r="I7" s="35">
+        <v>1</v>
+      </c>
+      <c r="J7" s="41" t="s">
+        <v>72</v>
+      </c>
+      <c r="K7" s="77">
+        <v>45696</v>
+      </c>
+      <c r="L7" s="41" t="s">
         <v>73</v>
       </c>
-      <c r="D7" s="41" t="s">
-        <v>123</v>
-      </c>
-      <c r="E7" s="34" t="s">
-        <v>157</v>
-      </c>
-      <c r="F7" s="41" t="s">
-        <v>109</v>
-      </c>
-      <c r="G7" s="34" t="s">
-        <v>162</v>
-      </c>
-      <c r="H7" s="44" t="s">
-        <v>120</v>
-      </c>
-      <c r="I7" s="36">
-        <v>1</v>
-      </c>
-      <c r="J7" s="42" t="s">
-        <v>74</v>
-      </c>
-      <c r="K7" s="78">
-        <v>45696</v>
-      </c>
-      <c r="L7" s="42" t="s">
-        <v>75</v>
-      </c>
-      <c r="M7" s="78" t="s">
-        <v>75</v>
-      </c>
-      <c r="N7" s="42" t="s">
-        <v>113</v>
-      </c>
-      <c r="O7" s="64"/>
+      <c r="M7" s="77" t="s">
+        <v>73</v>
+      </c>
+      <c r="N7" s="41" t="s">
+        <v>111</v>
+      </c>
+      <c r="O7" s="63"/>
     </row>
     <row r="8" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="39">
+      <c r="A8" s="38">
         <v>7</v>
       </c>
-      <c r="B8" s="35" t="s">
-        <v>127</v>
-      </c>
-      <c r="C8" s="34" t="s">
+      <c r="B8" s="34" t="s">
+        <v>125</v>
+      </c>
+      <c r="C8" s="33" t="s">
+        <v>74</v>
+      </c>
+      <c r="D8" s="40" t="s">
+        <v>121</v>
+      </c>
+      <c r="E8" s="33" t="s">
+        <v>156</v>
+      </c>
+      <c r="F8" s="40" t="s">
+        <v>107</v>
+      </c>
+      <c r="G8" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="H8" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="D8" s="41" t="s">
-        <v>123</v>
-      </c>
-      <c r="E8" s="34" t="s">
-        <v>158</v>
-      </c>
-      <c r="F8" s="41" t="s">
-        <v>109</v>
-      </c>
-      <c r="G8" s="34" t="s">
+      <c r="I8" s="36">
+        <v>1</v>
+      </c>
+      <c r="J8" s="41" t="s">
         <v>77</v>
       </c>
-      <c r="H8" s="34" t="s">
+      <c r="K8" s="77">
+        <v>45677</v>
+      </c>
+      <c r="L8" s="41" t="s">
         <v>78</v>
       </c>
-      <c r="I8" s="37">
-        <v>1</v>
-      </c>
-      <c r="J8" s="42" t="s">
-        <v>79</v>
-      </c>
-      <c r="K8" s="78">
-        <v>45677</v>
-      </c>
-      <c r="L8" s="42" t="s">
-        <v>80</v>
-      </c>
-      <c r="M8" s="78" t="s">
-        <v>75</v>
-      </c>
-      <c r="N8" s="42" t="s">
-        <v>117</v>
-      </c>
-      <c r="O8" s="64"/>
+      <c r="M8" s="77" t="s">
+        <v>73</v>
+      </c>
+      <c r="N8" s="41" t="s">
+        <v>115</v>
+      </c>
+      <c r="O8" s="63"/>
     </row>
     <row r="9" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="37">
+      <c r="A9" s="36">
         <v>8</v>
       </c>
-      <c r="B9" s="35" t="s">
-        <v>127</v>
-      </c>
-      <c r="C9" s="34" t="s">
+      <c r="B9" s="34" t="s">
+        <v>125</v>
+      </c>
+      <c r="C9" s="33" t="s">
+        <v>79</v>
+      </c>
+      <c r="D9" s="40" t="s">
+        <v>121</v>
+      </c>
+      <c r="E9" s="33" t="s">
+        <v>156</v>
+      </c>
+      <c r="F9" s="40" t="s">
+        <v>107</v>
+      </c>
+      <c r="G9" s="33" t="s">
+        <v>119</v>
+      </c>
+      <c r="H9" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="I9" s="36">
+        <v>1</v>
+      </c>
+      <c r="J9" s="41" t="s">
         <v>81</v>
       </c>
-      <c r="D9" s="41" t="s">
-        <v>123</v>
-      </c>
-      <c r="E9" s="34" t="s">
-        <v>158</v>
-      </c>
-      <c r="F9" s="41" t="s">
-        <v>109</v>
-      </c>
-      <c r="G9" s="34" t="s">
-        <v>121</v>
-      </c>
-      <c r="H9" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="I9" s="37">
-        <v>1</v>
-      </c>
-      <c r="J9" s="42" t="s">
-        <v>83</v>
-      </c>
-      <c r="K9" s="78">
+      <c r="K9" s="77">
         <v>45702</v>
       </c>
-      <c r="L9" s="43">
+      <c r="L9" s="42">
         <v>241015397</v>
       </c>
-      <c r="M9" s="78">
+      <c r="M9" s="77">
         <v>45717</v>
       </c>
-      <c r="N9" s="42" t="s">
-        <v>117</v>
-      </c>
-      <c r="O9" s="64"/>
+      <c r="N9" s="41" t="s">
+        <v>115</v>
+      </c>
+      <c r="O9" s="63"/>
     </row>
     <row r="10" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="39">
+      <c r="A10" s="38">
         <v>9</v>
       </c>
-      <c r="B10" s="35" t="s">
-        <v>128</v>
-      </c>
-      <c r="C10" s="34" t="s">
+      <c r="B10" s="34" t="s">
+        <v>126</v>
+      </c>
+      <c r="C10" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="D10" s="40" t="s">
+        <v>121</v>
+      </c>
+      <c r="E10" s="40" t="s">
+        <v>157</v>
+      </c>
+      <c r="F10" s="40" t="s">
+        <v>107</v>
+      </c>
+      <c r="G10" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="H10" s="33" t="s">
         <v>84</v>
       </c>
-      <c r="D10" s="41" t="s">
-        <v>123</v>
-      </c>
-      <c r="E10" s="41" t="s">
-        <v>159</v>
-      </c>
-      <c r="F10" s="41" t="s">
-        <v>109</v>
-      </c>
-      <c r="G10" s="34" t="s">
+      <c r="I10" s="36">
+        <v>1</v>
+      </c>
+      <c r="J10" s="41" t="s">
         <v>85</v>
       </c>
-      <c r="H10" s="34" t="s">
-        <v>86</v>
-      </c>
-      <c r="I10" s="37">
-        <v>1</v>
-      </c>
-      <c r="J10" s="42" t="s">
-        <v>87</v>
-      </c>
-      <c r="K10" s="78">
+      <c r="K10" s="77">
         <v>45702</v>
       </c>
-      <c r="L10" s="43">
+      <c r="L10" s="42">
         <v>241015396</v>
       </c>
-      <c r="M10" s="78">
+      <c r="M10" s="77">
         <v>45717</v>
       </c>
-      <c r="N10" s="42" t="s">
-        <v>117</v>
-      </c>
-      <c r="O10" s="64" t="s">
-        <v>145</v>
+      <c r="N10" s="41" t="s">
+        <v>115</v>
+      </c>
+      <c r="O10" s="63" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="11" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="37">
+      <c r="A11" s="36">
         <v>10</v>
       </c>
-      <c r="B11" s="34" t="s">
-        <v>122</v>
-      </c>
-      <c r="C11" s="34" t="s">
+      <c r="B11" s="33" t="s">
+        <v>120</v>
+      </c>
+      <c r="C11" s="33" t="s">
+        <v>86</v>
+      </c>
+      <c r="D11" s="40" t="s">
+        <v>121</v>
+      </c>
+      <c r="E11" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="F11" s="40" t="s">
+        <v>107</v>
+      </c>
+      <c r="G11" s="33" t="s">
+        <v>159</v>
+      </c>
+      <c r="H11" s="33" t="s">
+        <v>87</v>
+      </c>
+      <c r="I11" s="36">
+        <v>1</v>
+      </c>
+      <c r="J11" s="41" t="s">
         <v>88</v>
       </c>
-      <c r="D11" s="41" t="s">
-        <v>123</v>
-      </c>
-      <c r="E11" s="34" t="s">
-        <v>155</v>
-      </c>
-      <c r="F11" s="41" t="s">
-        <v>109</v>
-      </c>
-      <c r="G11" s="34" t="s">
-        <v>161</v>
-      </c>
-      <c r="H11" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="I11" s="37">
-        <v>1</v>
-      </c>
-      <c r="J11" s="42" t="s">
-        <v>90</v>
-      </c>
-      <c r="K11" s="78">
+      <c r="K11" s="77">
         <v>45709</v>
       </c>
-      <c r="L11" s="43">
+      <c r="L11" s="42">
         <v>241015532</v>
       </c>
-      <c r="M11" s="78">
+      <c r="M11" s="77">
         <v>45719</v>
       </c>
-      <c r="N11" s="42" t="s">
-        <v>117</v>
-      </c>
-      <c r="O11" s="64"/>
+      <c r="N11" s="41" t="s">
+        <v>115</v>
+      </c>
+      <c r="O11" s="63"/>
     </row>
     <row r="12" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="39">
+      <c r="A12" s="38">
         <v>11</v>
       </c>
-      <c r="B12" s="34" t="s">
-        <v>122</v>
-      </c>
-      <c r="C12" s="34" t="s">
+      <c r="B12" s="33" t="s">
+        <v>120</v>
+      </c>
+      <c r="C12" s="33" t="s">
+        <v>89</v>
+      </c>
+      <c r="D12" s="40" t="s">
+        <v>121</v>
+      </c>
+      <c r="E12" s="33" t="s">
+        <v>156</v>
+      </c>
+      <c r="F12" s="40" t="s">
+        <v>107</v>
+      </c>
+      <c r="G12" s="33" t="s">
+        <v>90</v>
+      </c>
+      <c r="H12" s="33" t="s">
         <v>91</v>
       </c>
-      <c r="D12" s="41" t="s">
-        <v>123</v>
-      </c>
-      <c r="E12" s="34" t="s">
-        <v>158</v>
-      </c>
-      <c r="F12" s="41" t="s">
-        <v>109</v>
-      </c>
-      <c r="G12" s="34" t="s">
+      <c r="I12" s="38">
+        <v>1</v>
+      </c>
+      <c r="J12" s="41" t="s">
         <v>92</v>
       </c>
-      <c r="H12" s="34" t="s">
-        <v>93</v>
-      </c>
-      <c r="I12" s="39">
-        <v>1</v>
-      </c>
-      <c r="J12" s="42" t="s">
-        <v>94</v>
-      </c>
-      <c r="K12" s="78">
+      <c r="K12" s="77">
         <v>45720</v>
       </c>
-      <c r="L12" s="43">
+      <c r="L12" s="42">
         <v>241016229</v>
       </c>
-      <c r="M12" s="78">
+      <c r="M12" s="77">
         <v>45735</v>
       </c>
-      <c r="N12" s="42" t="s">
-        <v>117</v>
-      </c>
-      <c r="O12" s="64"/>
+      <c r="N12" s="41" t="s">
+        <v>115</v>
+      </c>
+      <c r="O12" s="63"/>
     </row>
     <row r="13" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="37">
+      <c r="A13" s="36">
         <v>12</v>
       </c>
-      <c r="B13" s="34" t="s">
-        <v>122</v>
-      </c>
-      <c r="C13" s="35" t="s">
-        <v>144</v>
-      </c>
-      <c r="D13" s="41" t="s">
-        <v>123</v>
-      </c>
-      <c r="E13" s="41" t="s">
-        <v>159</v>
-      </c>
-      <c r="F13" s="41" t="s">
-        <v>109</v>
-      </c>
-      <c r="G13" s="34" t="s">
+      <c r="B13" s="33" t="s">
+        <v>120</v>
+      </c>
+      <c r="C13" s="34" t="s">
+        <v>142</v>
+      </c>
+      <c r="D13" s="40" t="s">
+        <v>121</v>
+      </c>
+      <c r="E13" s="40" t="s">
+        <v>157</v>
+      </c>
+      <c r="F13" s="40" t="s">
+        <v>107</v>
+      </c>
+      <c r="G13" s="33" t="s">
+        <v>93</v>
+      </c>
+      <c r="H13" s="33" t="s">
+        <v>94</v>
+      </c>
+      <c r="I13" s="36">
+        <v>1</v>
+      </c>
+      <c r="J13" s="41" t="s">
         <v>95</v>
       </c>
-      <c r="H13" s="34" t="s">
+      <c r="K13" s="77">
+        <v>45825</v>
+      </c>
+      <c r="L13" s="41" t="s">
         <v>96</v>
       </c>
-      <c r="I13" s="37">
-        <v>1</v>
-      </c>
-      <c r="J13" s="42" t="s">
-        <v>97</v>
-      </c>
-      <c r="K13" s="78">
-        <v>45825</v>
-      </c>
-      <c r="L13" s="42" t="s">
-        <v>98</v>
-      </c>
-      <c r="M13" s="78" t="s">
-        <v>75</v>
-      </c>
-      <c r="N13" s="42" t="s">
-        <v>117</v>
-      </c>
-      <c r="O13" s="64"/>
+      <c r="M13" s="77" t="s">
+        <v>73</v>
+      </c>
+      <c r="N13" s="41" t="s">
+        <v>115</v>
+      </c>
+      <c r="O13" s="63"/>
     </row>
     <row r="14" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="39">
+      <c r="A14" s="38">
         <v>13</v>
       </c>
-      <c r="B14" s="35" t="s">
-        <v>129</v>
-      </c>
-      <c r="C14" s="34" t="s">
+      <c r="B14" s="34" t="s">
+        <v>127</v>
+      </c>
+      <c r="C14" s="33" t="s">
+        <v>52</v>
+      </c>
+      <c r="D14" s="40" t="s">
+        <v>121</v>
+      </c>
+      <c r="E14" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="F14" s="40" t="s">
+        <v>107</v>
+      </c>
+      <c r="G14" s="33" t="s">
+        <v>53</v>
+      </c>
+      <c r="H14" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="D14" s="41" t="s">
-        <v>123</v>
-      </c>
-      <c r="E14" s="34" t="s">
-        <v>157</v>
-      </c>
-      <c r="F14" s="41" t="s">
-        <v>109</v>
-      </c>
-      <c r="G14" s="34" t="s">
+      <c r="I14" s="36">
+        <v>1</v>
+      </c>
+      <c r="J14" s="41" t="s">
         <v>55</v>
       </c>
-      <c r="H14" s="34" t="s">
-        <v>56</v>
-      </c>
-      <c r="I14" s="37">
-        <v>1</v>
-      </c>
-      <c r="J14" s="42" t="s">
-        <v>57</v>
-      </c>
-      <c r="K14" s="78">
+      <c r="K14" s="77">
         <v>45432</v>
       </c>
-      <c r="L14" s="38">
+      <c r="L14" s="37">
         <v>241001943</v>
       </c>
-      <c r="M14" s="78">
+      <c r="M14" s="77">
         <v>45453</v>
       </c>
-      <c r="N14" s="42" t="s">
-        <v>117</v>
-      </c>
-      <c r="O14" s="64"/>
+      <c r="N14" s="41" t="s">
+        <v>115</v>
+      </c>
+      <c r="O14" s="63"/>
     </row>
     <row r="15" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="37">
+      <c r="A15" s="36">
         <v>14</v>
       </c>
-      <c r="B15" s="34" t="s">
-        <v>129</v>
-      </c>
-      <c r="C15" s="34" t="s">
+      <c r="B15" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="C15" s="33" t="s">
+        <v>97</v>
+      </c>
+      <c r="D15" s="40" t="s">
+        <v>121</v>
+      </c>
+      <c r="E15" s="33" t="s">
+        <v>156</v>
+      </c>
+      <c r="F15" s="40" t="s">
+        <v>107</v>
+      </c>
+      <c r="G15" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="H15" s="33" t="s">
         <v>99</v>
       </c>
-      <c r="D15" s="41" t="s">
-        <v>123</v>
-      </c>
-      <c r="E15" s="34" t="s">
-        <v>158</v>
-      </c>
-      <c r="F15" s="41" t="s">
-        <v>109</v>
-      </c>
-      <c r="G15" s="34" t="s">
+      <c r="I15" s="35">
+        <v>1</v>
+      </c>
+      <c r="J15" s="41" t="s">
         <v>100</v>
       </c>
-      <c r="H15" s="34" t="s">
-        <v>101</v>
-      </c>
-      <c r="I15" s="36">
-        <v>1</v>
-      </c>
-      <c r="J15" s="42" t="s">
-        <v>102</v>
-      </c>
-      <c r="K15" s="78">
+      <c r="K15" s="77">
         <v>45675</v>
       </c>
-      <c r="L15" s="43">
+      <c r="L15" s="42">
         <v>251009621</v>
       </c>
-      <c r="M15" s="78">
+      <c r="M15" s="77">
         <v>45874</v>
       </c>
-      <c r="N15" s="42" t="s">
-        <v>113</v>
-      </c>
-      <c r="O15" s="64"/>
+      <c r="N15" s="41" t="s">
+        <v>111</v>
+      </c>
+      <c r="O15" s="63"/>
     </row>
     <row r="16" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="39">
+      <c r="A16" s="38">
         <v>15</v>
       </c>
-      <c r="B16" s="35" t="s">
-        <v>129</v>
-      </c>
-      <c r="C16" s="34" t="s">
-        <v>160</v>
-      </c>
-      <c r="D16" s="41" t="s">
-        <v>123</v>
-      </c>
-      <c r="E16" s="34" t="s">
+      <c r="B16" s="34" t="s">
+        <v>127</v>
+      </c>
+      <c r="C16" s="33" t="s">
         <v>158</v>
       </c>
-      <c r="F16" s="41" t="s">
-        <v>109</v>
-      </c>
-      <c r="G16" s="34" t="s">
+      <c r="D16" s="40" t="s">
+        <v>121</v>
+      </c>
+      <c r="E16" s="33" t="s">
+        <v>156</v>
+      </c>
+      <c r="F16" s="40" t="s">
+        <v>107</v>
+      </c>
+      <c r="G16" s="33" t="s">
+        <v>101</v>
+      </c>
+      <c r="H16" s="33" t="s">
+        <v>102</v>
+      </c>
+      <c r="I16" s="35">
+        <v>1</v>
+      </c>
+      <c r="J16" s="41" t="s">
         <v>103</v>
       </c>
-      <c r="H16" s="34" t="s">
-        <v>104</v>
-      </c>
-      <c r="I16" s="36">
-        <v>1</v>
-      </c>
-      <c r="J16" s="42" t="s">
-        <v>105</v>
-      </c>
-      <c r="K16" s="78">
+      <c r="K16" s="77">
         <v>45897</v>
       </c>
-      <c r="L16" s="42" t="s">
-        <v>50</v>
-      </c>
-      <c r="M16" s="78" t="s">
-        <v>98</v>
-      </c>
-      <c r="N16" s="42" t="s">
-        <v>117</v>
-      </c>
-      <c r="O16" s="64"/>
+      <c r="L16" s="41" t="s">
+        <v>48</v>
+      </c>
+      <c r="M16" s="77" t="s">
+        <v>96</v>
+      </c>
+      <c r="N16" s="41" t="s">
+        <v>115</v>
+      </c>
+      <c r="O16" s="63"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="64"/>
-      <c r="B17" s="64"/>
-      <c r="C17" s="64"/>
-      <c r="D17" s="64"/>
-      <c r="E17" s="64"/>
-      <c r="F17" s="64"/>
-      <c r="G17" s="64"/>
-      <c r="H17" s="64"/>
-      <c r="I17" s="64"/>
-      <c r="J17" s="64"/>
-      <c r="K17" s="79"/>
-      <c r="L17" s="64"/>
-      <c r="M17" s="79"/>
-      <c r="N17" s="64"/>
-      <c r="O17" s="64"/>
+      <c r="A17" s="63"/>
+      <c r="B17" s="63"/>
+      <c r="C17" s="63"/>
+      <c r="D17" s="63"/>
+      <c r="E17" s="63"/>
+      <c r="F17" s="63"/>
+      <c r="G17" s="63"/>
+      <c r="H17" s="63"/>
+      <c r="I17" s="63"/>
+      <c r="J17" s="63"/>
+      <c r="K17" s="78"/>
+      <c r="L17" s="63"/>
+      <c r="M17" s="78"/>
+      <c r="N17" s="63"/>
+      <c r="O17" s="63"/>
     </row>
   </sheetData>
   <phoneticPr fontId="24" type="noConversion"/>
@@ -8233,575 +8205,575 @@
   <dimension ref="A1:P19"/>
   <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.77734375" style="70" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.33203125" style="70" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.109375" style="70" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12" style="70" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.77734375" style="70" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.6640625" style="70" customWidth="1"/>
-    <col min="7" max="7" width="25.44140625" style="70" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="31.6640625" style="70" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="4.6640625" style="70" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22" style="70" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.6640625" style="80" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.33203125" style="70" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.33203125" style="80" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.33203125" style="70" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.33203125" style="70" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.33203125" style="70"/>
+    <col min="1" max="1" width="6.77734375" style="69" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.33203125" style="69" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.109375" style="69" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12" style="69" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.77734375" style="69" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" style="69" customWidth="1"/>
+    <col min="7" max="7" width="25.44140625" style="69" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="31.6640625" style="69" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.6640625" style="69" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22" style="69" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.6640625" style="79" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.33203125" style="69" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.33203125" style="79" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.33203125" style="69" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.33203125" style="69" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.33203125" style="69"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="49" t="s">
+    <row r="1" spans="1:16" s="65" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="48" t="s">
+        <v>128</v>
+      </c>
+      <c r="B1" s="86" t="s">
+        <v>162</v>
+      </c>
+      <c r="C1" s="61" t="s">
+        <v>104</v>
+      </c>
+      <c r="D1" s="50" t="s">
+        <v>122</v>
+      </c>
+      <c r="E1" s="74" t="s">
+        <v>144</v>
+      </c>
+      <c r="F1" s="51" t="s">
+        <v>129</v>
+      </c>
+      <c r="G1" s="51" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="51" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" s="52" t="s">
         <v>130</v>
       </c>
-      <c r="B1" s="88" t="s">
-        <v>164</v>
-      </c>
-      <c r="C1" s="62" t="s">
-        <v>106</v>
-      </c>
-      <c r="D1" s="51" t="s">
-        <v>124</v>
-      </c>
-      <c r="E1" s="75" t="s">
-        <v>146</v>
-      </c>
-      <c r="F1" s="52" t="s">
+      <c r="J1" s="51" t="s">
         <v>131</v>
       </c>
-      <c r="G1" s="52" t="s">
-        <v>2</v>
-      </c>
-      <c r="H1" s="52" t="s">
-        <v>3</v>
-      </c>
-      <c r="I1" s="53" t="s">
+      <c r="K1" s="75" t="s">
         <v>132</v>
       </c>
-      <c r="J1" s="52" t="s">
+      <c r="L1" s="48" t="s">
         <v>133</v>
       </c>
-      <c r="K1" s="76" t="s">
+      <c r="M1" s="75" t="s">
         <v>134</v>
       </c>
-      <c r="L1" s="49" t="s">
-        <v>135</v>
-      </c>
-      <c r="M1" s="76" t="s">
-        <v>136</v>
-      </c>
-      <c r="N1" s="52" t="s">
+      <c r="N1" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="O1" s="18" t="s">
-        <v>107</v>
+      <c r="O1" s="17" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="67">
+      <c r="A2" s="66">
         <v>1</v>
       </c>
-      <c r="B2" s="54" t="s">
+      <c r="B2" s="53" t="s">
+        <v>106</v>
+      </c>
+      <c r="C2" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="D2" s="32" t="s">
+        <v>121</v>
+      </c>
+      <c r="E2" s="32" t="s">
+        <v>153</v>
+      </c>
+      <c r="F2" s="54" t="s">
+        <v>107</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="H2" s="32" t="s">
         <v>110</v>
       </c>
-      <c r="D2" s="33" t="s">
-        <v>123</v>
-      </c>
-      <c r="E2" s="33" t="s">
-        <v>155</v>
-      </c>
-      <c r="F2" s="55" t="s">
-        <v>109</v>
-      </c>
-      <c r="G2" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="H2" s="33" t="s">
-        <v>112</v>
-      </c>
-      <c r="I2" s="46">
+      <c r="I2" s="45">
         <v>1</v>
       </c>
-      <c r="J2" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="K2" s="81">
+      <c r="J2" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="K2" s="80">
         <v>44629</v>
       </c>
-      <c r="L2" s="47">
+      <c r="L2" s="46">
         <v>241000273</v>
       </c>
-      <c r="M2" s="77">
+      <c r="M2" s="76">
         <v>45405</v>
       </c>
-      <c r="N2" s="90" t="s">
-        <v>165</v>
-      </c>
-      <c r="O2" s="68"/>
-      <c r="P2" s="69"/>
+      <c r="N2" s="88" t="s">
+        <v>163</v>
+      </c>
+      <c r="O2" s="67"/>
+      <c r="P2" s="68"/>
     </row>
     <row r="3" spans="1:16" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="71">
+      <c r="A3" s="70">
         <v>2</v>
       </c>
-      <c r="B3" s="54" t="s">
-        <v>108</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="D3" s="33" t="s">
-        <v>123</v>
-      </c>
-      <c r="E3" s="33" t="s">
-        <v>155</v>
-      </c>
-      <c r="F3" s="55" t="s">
-        <v>109</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="H3" s="33" t="s">
+      <c r="B3" s="53" t="s">
+        <v>106</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="D3" s="32" t="s">
+        <v>121</v>
+      </c>
+      <c r="E3" s="32" t="s">
+        <v>153</v>
+      </c>
+      <c r="F3" s="54" t="s">
+        <v>107</v>
+      </c>
+      <c r="G3" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="I3" s="46">
+      <c r="H3" s="32" t="s">
+        <v>136</v>
+      </c>
+      <c r="I3" s="45">
         <v>1</v>
       </c>
-      <c r="J3" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="K3" s="81">
+      <c r="J3" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="K3" s="80">
         <v>45386</v>
       </c>
-      <c r="L3" s="47">
+      <c r="L3" s="46">
         <v>243000275</v>
       </c>
-      <c r="M3" s="77">
+      <c r="M3" s="76">
         <v>45404</v>
       </c>
-      <c r="N3" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="O3" s="68"/>
-      <c r="P3" s="69"/>
+      <c r="N3" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="O3" s="67"/>
+      <c r="P3" s="68"/>
     </row>
     <row r="4" spans="1:16" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="71">
+      <c r="A4" s="70">
         <v>2</v>
       </c>
-      <c r="B4" s="54" t="s">
-        <v>108</v>
-      </c>
-      <c r="C4" s="11" t="s">
+      <c r="B4" s="53" t="s">
+        <v>106</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="D4" s="32" t="s">
+        <v>121</v>
+      </c>
+      <c r="E4" s="32" t="s">
+        <v>153</v>
+      </c>
+      <c r="F4" s="54" t="s">
+        <v>107</v>
+      </c>
+      <c r="G4" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="D4" s="33" t="s">
-        <v>123</v>
-      </c>
-      <c r="E4" s="33" t="s">
-        <v>155</v>
-      </c>
-      <c r="F4" s="55" t="s">
-        <v>109</v>
-      </c>
-      <c r="G4" s="11" t="s">
+      <c r="H4" s="32" t="s">
+        <v>136</v>
+      </c>
+      <c r="I4" s="45">
+        <v>1</v>
+      </c>
+      <c r="J4" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="H4" s="33" t="s">
-        <v>138</v>
-      </c>
-      <c r="I4" s="46">
-        <v>1</v>
-      </c>
-      <c r="J4" s="17" t="s">
-        <v>153</v>
-      </c>
-      <c r="K4" s="81">
+      <c r="K4" s="80">
         <v>45752</v>
       </c>
-      <c r="L4" s="47"/>
-      <c r="M4" s="77"/>
-      <c r="N4" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="O4" s="68"/>
-      <c r="P4" s="69"/>
+      <c r="L4" s="46"/>
+      <c r="M4" s="76"/>
+      <c r="N4" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="O4" s="67"/>
+      <c r="P4" s="68"/>
     </row>
     <row r="5" spans="1:16" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="71">
+      <c r="A5" s="70">
         <v>2</v>
       </c>
-      <c r="B5" s="54" t="s">
-        <v>108</v>
-      </c>
-      <c r="C5" s="11" t="s">
+      <c r="B5" s="53" t="s">
+        <v>106</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="D5" s="32" t="s">
+        <v>121</v>
+      </c>
+      <c r="E5" s="32" t="s">
+        <v>153</v>
+      </c>
+      <c r="F5" s="54" t="s">
+        <v>107</v>
+      </c>
+      <c r="G5" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="D5" s="33" t="s">
-        <v>123</v>
-      </c>
-      <c r="E5" s="33" t="s">
-        <v>155</v>
-      </c>
-      <c r="F5" s="55" t="s">
-        <v>109</v>
-      </c>
-      <c r="G5" s="11" t="s">
+      <c r="H5" s="32" t="s">
+        <v>136</v>
+      </c>
+      <c r="I5" s="45">
+        <v>1</v>
+      </c>
+      <c r="J5" s="16" t="s">
         <v>152</v>
       </c>
-      <c r="H5" s="33" t="s">
-        <v>138</v>
-      </c>
-      <c r="I5" s="46">
-        <v>1</v>
-      </c>
-      <c r="J5" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="K5" s="81">
+      <c r="K5" s="80">
         <v>45295</v>
       </c>
-      <c r="L5" s="47">
+      <c r="L5" s="46">
         <v>243000645</v>
       </c>
-      <c r="M5" s="77">
+      <c r="M5" s="76">
         <v>45344</v>
       </c>
-      <c r="N5" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="O5" s="68"/>
-      <c r="P5" s="69"/>
+      <c r="N5" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="O5" s="67"/>
+      <c r="P5" s="68"/>
     </row>
     <row r="6" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="56">
+      <c r="A6" s="55">
         <v>3</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D6" s="32" t="s">
+        <v>121</v>
+      </c>
+      <c r="E6" s="32" t="s">
+        <v>153</v>
+      </c>
+      <c r="F6" s="54" t="s">
+        <v>107</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="I6" s="47">
+        <v>1</v>
+      </c>
+      <c r="J6" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C6" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="D6" s="33" t="s">
-        <v>123</v>
-      </c>
-      <c r="E6" s="33" t="s">
-        <v>155</v>
-      </c>
-      <c r="F6" s="55" t="s">
-        <v>109</v>
-      </c>
-      <c r="G6" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="H6" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="I6" s="48">
-        <v>1</v>
-      </c>
-      <c r="J6" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="K6" s="81">
+      <c r="K6" s="80">
         <v>45208</v>
       </c>
-      <c r="L6" s="47">
+      <c r="L6" s="46">
         <v>231011060</v>
       </c>
-      <c r="M6" s="77">
+      <c r="M6" s="76">
         <v>45921</v>
       </c>
-      <c r="N6" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="O6" s="68"/>
-      <c r="P6" s="69"/>
+      <c r="N6" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="O6" s="67"/>
+      <c r="P6" s="68"/>
     </row>
     <row r="7" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="57">
+      <c r="A7" s="56">
         <v>4</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" s="32" t="s">
+        <v>121</v>
+      </c>
+      <c r="E7" s="32" t="s">
+        <v>156</v>
+      </c>
+      <c r="F7" s="54" t="s">
+        <v>107</v>
+      </c>
+      <c r="G7" s="15">
+        <v>2920.0019080000002</v>
+      </c>
+      <c r="H7" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="I7" s="57">
+        <v>1</v>
+      </c>
+      <c r="J7" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="D7" s="33" t="s">
-        <v>123</v>
-      </c>
-      <c r="E7" s="33" t="s">
-        <v>158</v>
-      </c>
-      <c r="F7" s="55" t="s">
-        <v>109</v>
-      </c>
-      <c r="G7" s="16">
-        <v>2920.0019080000002</v>
-      </c>
-      <c r="H7" s="11" t="s">
+      <c r="K7" s="80">
+        <v>45388</v>
+      </c>
+      <c r="L7" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="I7" s="58">
-        <v>1</v>
-      </c>
-      <c r="J7" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="K7" s="81">
-        <v>45388</v>
-      </c>
-      <c r="L7" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="M7" s="77" t="s">
-        <v>50</v>
-      </c>
-      <c r="N7" s="89" t="s">
-        <v>165</v>
-      </c>
-      <c r="O7" s="72"/>
-      <c r="P7" s="73"/>
+      <c r="M7" s="76" t="s">
+        <v>48</v>
+      </c>
+      <c r="N7" s="87" t="s">
+        <v>163</v>
+      </c>
+      <c r="O7" s="71"/>
+      <c r="P7" s="72"/>
     </row>
     <row r="8" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="59">
+      <c r="A8" s="58">
         <v>5</v>
       </c>
-      <c r="B8" s="54" t="s">
-        <v>128</v>
-      </c>
-      <c r="C8" s="11" t="s">
+      <c r="B8" s="53" t="s">
+        <v>126</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="32" t="s">
+        <v>121</v>
+      </c>
+      <c r="E8" s="32" t="s">
+        <v>157</v>
+      </c>
+      <c r="F8" s="54" t="s">
+        <v>107</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="H8" s="32" t="s">
+        <v>140</v>
+      </c>
+      <c r="I8" s="47">
+        <v>1</v>
+      </c>
+      <c r="J8" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="D8" s="33" t="s">
-        <v>123</v>
-      </c>
-      <c r="E8" s="33" t="s">
-        <v>159</v>
-      </c>
-      <c r="F8" s="55" t="s">
-        <v>109</v>
-      </c>
-      <c r="G8" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="H8" s="33" t="s">
-        <v>142</v>
-      </c>
-      <c r="I8" s="48">
-        <v>1</v>
-      </c>
-      <c r="J8" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="K8" s="81">
+      <c r="K8" s="80">
         <v>45386</v>
       </c>
-      <c r="L8" s="60">
+      <c r="L8" s="59">
         <v>241000273</v>
       </c>
-      <c r="M8" s="77">
+      <c r="M8" s="76">
         <v>45404</v>
       </c>
-      <c r="N8" s="89" t="s">
-        <v>113</v>
-      </c>
-      <c r="O8" s="72"/>
-      <c r="P8" s="73"/>
+      <c r="N8" s="87" t="s">
+        <v>111</v>
+      </c>
+      <c r="O8" s="71"/>
+      <c r="P8" s="72"/>
     </row>
     <row r="9" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="39"/>
-      <c r="B9" s="34"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="41"/>
-      <c r="G9" s="34"/>
-      <c r="H9" s="44"/>
-      <c r="I9" s="36"/>
-      <c r="J9" s="42"/>
-      <c r="K9" s="78"/>
-      <c r="L9" s="42"/>
-      <c r="M9" s="78"/>
-      <c r="N9" s="42"/>
-      <c r="O9" s="64"/>
+      <c r="A9" s="38"/>
+      <c r="B9" s="33"/>
+      <c r="C9" s="33"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="40"/>
+      <c r="G9" s="33"/>
+      <c r="H9" s="43"/>
+      <c r="I9" s="35"/>
+      <c r="J9" s="41"/>
+      <c r="K9" s="77"/>
+      <c r="L9" s="41"/>
+      <c r="M9" s="77"/>
+      <c r="N9" s="41"/>
+      <c r="O9" s="63"/>
     </row>
     <row r="10" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="37"/>
-      <c r="B10" s="35"/>
-      <c r="C10" s="34"/>
-      <c r="D10" s="34"/>
-      <c r="E10" s="34"/>
-      <c r="F10" s="41"/>
-      <c r="G10" s="34"/>
-      <c r="H10" s="34"/>
-      <c r="I10" s="37"/>
-      <c r="J10" s="42"/>
-      <c r="K10" s="78"/>
-      <c r="L10" s="42"/>
-      <c r="M10" s="78"/>
-      <c r="N10" s="42"/>
-      <c r="O10" s="64"/>
+      <c r="A10" s="36"/>
+      <c r="B10" s="34"/>
+      <c r="C10" s="33"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="33"/>
+      <c r="F10" s="40"/>
+      <c r="G10" s="33"/>
+      <c r="H10" s="33"/>
+      <c r="I10" s="36"/>
+      <c r="J10" s="41"/>
+      <c r="K10" s="77"/>
+      <c r="L10" s="41"/>
+      <c r="M10" s="77"/>
+      <c r="N10" s="41"/>
+      <c r="O10" s="63"/>
     </row>
     <row r="11" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="36"/>
-      <c r="B11" s="35"/>
-      <c r="C11" s="34"/>
-      <c r="D11" s="41"/>
-      <c r="E11" s="41"/>
-      <c r="F11" s="41"/>
-      <c r="G11" s="34"/>
-      <c r="H11" s="34"/>
-      <c r="I11" s="37"/>
-      <c r="J11" s="42"/>
-      <c r="K11" s="78"/>
-      <c r="L11" s="43"/>
-      <c r="M11" s="78"/>
-      <c r="N11" s="42"/>
-      <c r="O11" s="64"/>
+      <c r="A11" s="35"/>
+      <c r="B11" s="34"/>
+      <c r="C11" s="33"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
+      <c r="G11" s="33"/>
+      <c r="H11" s="33"/>
+      <c r="I11" s="36"/>
+      <c r="J11" s="41"/>
+      <c r="K11" s="77"/>
+      <c r="L11" s="42"/>
+      <c r="M11" s="77"/>
+      <c r="N11" s="41"/>
+      <c r="O11" s="63"/>
     </row>
     <row r="12" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="37"/>
-      <c r="B12" s="35"/>
-      <c r="C12" s="34"/>
-      <c r="D12" s="41"/>
-      <c r="E12" s="41"/>
-      <c r="F12" s="41"/>
-      <c r="G12" s="34"/>
-      <c r="H12" s="34"/>
-      <c r="I12" s="37"/>
-      <c r="J12" s="42"/>
-      <c r="K12" s="78"/>
-      <c r="L12" s="43"/>
-      <c r="M12" s="78"/>
-      <c r="N12" s="42"/>
-      <c r="O12" s="64"/>
+      <c r="A12" s="36"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="40"/>
+      <c r="E12" s="40"/>
+      <c r="F12" s="40"/>
+      <c r="G12" s="33"/>
+      <c r="H12" s="33"/>
+      <c r="I12" s="36"/>
+      <c r="J12" s="41"/>
+      <c r="K12" s="77"/>
+      <c r="L12" s="42"/>
+      <c r="M12" s="77"/>
+      <c r="N12" s="41"/>
+      <c r="O12" s="63"/>
     </row>
     <row r="13" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="37"/>
-      <c r="B13" s="34"/>
-      <c r="C13" s="34"/>
-      <c r="D13" s="34"/>
-      <c r="E13" s="34"/>
-      <c r="F13" s="41"/>
-      <c r="G13" s="34"/>
-      <c r="H13" s="34"/>
-      <c r="I13" s="37"/>
-      <c r="J13" s="42"/>
-      <c r="K13" s="78"/>
-      <c r="L13" s="43"/>
-      <c r="M13" s="78"/>
-      <c r="N13" s="42"/>
-      <c r="O13" s="64"/>
+      <c r="A13" s="36"/>
+      <c r="B13" s="33"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="40"/>
+      <c r="G13" s="33"/>
+      <c r="H13" s="33"/>
+      <c r="I13" s="36"/>
+      <c r="J13" s="41"/>
+      <c r="K13" s="77"/>
+      <c r="L13" s="42"/>
+      <c r="M13" s="77"/>
+      <c r="N13" s="41"/>
+      <c r="O13" s="63"/>
     </row>
     <row r="14" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="34"/>
-      <c r="B14" s="34"/>
-      <c r="C14" s="40"/>
-      <c r="D14" s="34"/>
-      <c r="E14" s="34"/>
-      <c r="F14" s="41"/>
-      <c r="G14" s="34"/>
-      <c r="H14" s="34"/>
-      <c r="I14" s="39"/>
-      <c r="J14" s="42"/>
-      <c r="K14" s="78"/>
-      <c r="L14" s="43"/>
-      <c r="M14" s="78"/>
-      <c r="N14" s="42"/>
-      <c r="O14" s="64"/>
+      <c r="A14" s="33"/>
+      <c r="B14" s="33"/>
+      <c r="C14" s="39"/>
+      <c r="D14" s="33"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="40"/>
+      <c r="G14" s="33"/>
+      <c r="H14" s="33"/>
+      <c r="I14" s="38"/>
+      <c r="J14" s="41"/>
+      <c r="K14" s="77"/>
+      <c r="L14" s="42"/>
+      <c r="M14" s="77"/>
+      <c r="N14" s="41"/>
+      <c r="O14" s="63"/>
     </row>
     <row r="15" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="36"/>
-      <c r="B15" s="34"/>
-      <c r="C15" s="35"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="41"/>
-      <c r="G15" s="34"/>
-      <c r="H15" s="34"/>
-      <c r="I15" s="37"/>
-      <c r="J15" s="42"/>
-      <c r="K15" s="78"/>
-      <c r="L15" s="42"/>
-      <c r="M15" s="78"/>
-      <c r="N15" s="42"/>
-      <c r="O15" s="64"/>
+      <c r="A15" s="35"/>
+      <c r="B15" s="33"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="33"/>
+      <c r="H15" s="33"/>
+      <c r="I15" s="36"/>
+      <c r="J15" s="41"/>
+      <c r="K15" s="77"/>
+      <c r="L15" s="41"/>
+      <c r="M15" s="77"/>
+      <c r="N15" s="41"/>
+      <c r="O15" s="63"/>
     </row>
     <row r="16" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="39"/>
-      <c r="B16" s="35"/>
-      <c r="C16" s="34"/>
-      <c r="D16" s="34"/>
-      <c r="E16" s="34"/>
-      <c r="F16" s="41"/>
-      <c r="G16" s="34"/>
-      <c r="H16" s="34"/>
-      <c r="I16" s="37"/>
-      <c r="J16" s="42"/>
-      <c r="K16" s="78"/>
-      <c r="L16" s="38"/>
-      <c r="M16" s="78"/>
-      <c r="N16" s="42"/>
-      <c r="O16" s="64"/>
+      <c r="A16" s="38"/>
+      <c r="B16" s="34"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="40"/>
+      <c r="G16" s="33"/>
+      <c r="H16" s="33"/>
+      <c r="I16" s="36"/>
+      <c r="J16" s="41"/>
+      <c r="K16" s="77"/>
+      <c r="L16" s="37"/>
+      <c r="M16" s="77"/>
+      <c r="N16" s="41"/>
+      <c r="O16" s="63"/>
     </row>
     <row r="17" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="36"/>
-      <c r="B17" s="34"/>
-      <c r="C17" s="34"/>
-      <c r="D17" s="34"/>
-      <c r="E17" s="34"/>
-      <c r="F17" s="41"/>
-      <c r="G17" s="34"/>
-      <c r="H17" s="34"/>
-      <c r="I17" s="36"/>
-      <c r="J17" s="42"/>
-      <c r="K17" s="78"/>
-      <c r="L17" s="43"/>
-      <c r="M17" s="78"/>
-      <c r="N17" s="42"/>
-      <c r="O17" s="64"/>
+      <c r="A17" s="35"/>
+      <c r="B17" s="33"/>
+      <c r="C17" s="33"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="40"/>
+      <c r="G17" s="33"/>
+      <c r="H17" s="33"/>
+      <c r="I17" s="35"/>
+      <c r="J17" s="41"/>
+      <c r="K17" s="77"/>
+      <c r="L17" s="42"/>
+      <c r="M17" s="77"/>
+      <c r="N17" s="41"/>
+      <c r="O17" s="63"/>
     </row>
     <row r="18" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="37"/>
-      <c r="B18" s="35"/>
-      <c r="C18" s="34"/>
-      <c r="D18" s="34"/>
-      <c r="E18" s="34"/>
-      <c r="F18" s="41"/>
-      <c r="G18" s="34"/>
-      <c r="H18" s="34"/>
-      <c r="I18" s="36"/>
-      <c r="J18" s="42"/>
-      <c r="K18" s="78"/>
-      <c r="L18" s="42"/>
-      <c r="M18" s="78"/>
-      <c r="N18" s="42"/>
-      <c r="O18" s="64"/>
+      <c r="A18" s="36"/>
+      <c r="B18" s="34"/>
+      <c r="C18" s="33"/>
+      <c r="D18" s="33"/>
+      <c r="E18" s="33"/>
+      <c r="F18" s="40"/>
+      <c r="G18" s="33"/>
+      <c r="H18" s="33"/>
+      <c r="I18" s="35"/>
+      <c r="J18" s="41"/>
+      <c r="K18" s="77"/>
+      <c r="L18" s="41"/>
+      <c r="M18" s="77"/>
+      <c r="N18" s="41"/>
+      <c r="O18" s="63"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="64"/>
-      <c r="B19" s="64"/>
-      <c r="C19" s="64"/>
-      <c r="D19" s="64"/>
-      <c r="E19" s="64"/>
-      <c r="F19" s="64"/>
-      <c r="G19" s="64"/>
-      <c r="H19" s="64"/>
-      <c r="I19" s="64"/>
-      <c r="J19" s="64"/>
-      <c r="K19" s="79"/>
-      <c r="L19" s="64"/>
-      <c r="M19" s="79"/>
-      <c r="N19" s="64"/>
-      <c r="O19" s="64"/>
+      <c r="A19" s="63"/>
+      <c r="B19" s="63"/>
+      <c r="C19" s="63"/>
+      <c r="D19" s="63"/>
+      <c r="E19" s="63"/>
+      <c r="F19" s="63"/>
+      <c r="G19" s="63"/>
+      <c r="H19" s="63"/>
+      <c r="I19" s="63"/>
+      <c r="J19" s="63"/>
+      <c r="K19" s="78"/>
+      <c r="L19" s="63"/>
+      <c r="M19" s="78"/>
+      <c r="N19" s="63"/>
+      <c r="O19" s="63"/>
     </row>
   </sheetData>
   <phoneticPr fontId="24" type="noConversion"/>
